--- a/sources/走遍中国_第四册_语法零基础版.xlsx
+++ b/sources/走遍中国_第四册_语法零基础版.xlsx
@@ -4,10 +4,11 @@
   <workbookPr/>
   <sheets>
     <sheet name="01_语法总表" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="02_学生英译汉练习版" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="03_按单元索引" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="04_使用说明" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="网站校对记录" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="进阶练习" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="02_学生英译汉练习版" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="03_按单元索引" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="04_使用说明" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="网站校对记录" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -16,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Carlito"/>
       <sz val="11"/>
@@ -27,8 +28,12 @@
       <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -63,6 +68,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF7257A4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008B2A1F"/>
       </patternFill>
     </fill>
   </fills>
@@ -129,7 +139,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -330,6 +340,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0"/>
@@ -7334,6 +7345,8160 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:L145"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="9" max="9"/>
+    <col width="50" customWidth="1" min="10" max="10"/>
+    <col width="50" customWidth="1" min="11" max="11"/>
+    <col width="40" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="76" t="inlineStr">
+        <is>
+          <t>语法编号</t>
+        </is>
+      </c>
+      <c r="B1" s="76" t="inlineStr">
+        <is>
+          <t>课次</t>
+        </is>
+      </c>
+      <c r="C1" s="76" t="inlineStr">
+        <is>
+          <t>题型</t>
+        </is>
+      </c>
+      <c r="D1" s="76" t="inlineStr">
+        <is>
+          <t>题干</t>
+        </is>
+      </c>
+      <c r="E1" s="76" t="inlineStr">
+        <is>
+          <t>选项A</t>
+        </is>
+      </c>
+      <c r="F1" s="76" t="inlineStr">
+        <is>
+          <t>选项B</t>
+        </is>
+      </c>
+      <c r="G1" s="76" t="inlineStr">
+        <is>
+          <t>选项C</t>
+        </is>
+      </c>
+      <c r="H1" s="76" t="inlineStr">
+        <is>
+          <t>选项D</t>
+        </is>
+      </c>
+      <c r="I1" s="76" t="inlineStr">
+        <is>
+          <t>答案</t>
+        </is>
+      </c>
+      <c r="J1" s="76" t="inlineStr">
+        <is>
+          <t>解析（中文）</t>
+        </is>
+      </c>
+      <c r="K1" s="76" t="inlineStr">
+        <is>
+          <t>解析（英文）</t>
+        </is>
+      </c>
+      <c r="L1" s="76" t="inlineStr">
+        <is>
+          <t>题干（英文）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U01-1</t>
+        </is>
+      </c>
+      <c r="B2" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="14" t="inlineStr">
+        <is>
+          <t>辨析</t>
+        </is>
+      </c>
+      <c r="D2" s="14" t="inlineStr">
+        <is>
+          <t>他来中国三年了，一句中文也___会说。</t>
+        </is>
+      </c>
+      <c r="E2" s="14" t="inlineStr">
+        <is>
+          <t>别</t>
+        </is>
+      </c>
+      <c r="F2" s="14" t="inlineStr">
+        <is>
+          <t>不</t>
+        </is>
+      </c>
+      <c r="G2" s="14" t="inlineStr">
+        <is>
+          <t>没</t>
+        </is>
+      </c>
+      <c r="H2" s="14" t="inlineStr">
+        <is>
+          <t>没有</t>
+        </is>
+      </c>
+      <c r="I2" s="14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J2" s="14" t="inlineStr">
+        <is>
+          <t>“会”表示能力，一般否定用“不”，所以是“一句也不会说”；“没”不能直接放在“会”前面。</t>
+        </is>
+      </c>
+      <c r="K2" s="14" t="inlineStr">
+        <is>
+          <t>会 (can) is negated with 不, so it is 一句也不会说; 没 cannot go before 会.</t>
+        </is>
+      </c>
+      <c r="L2" s="14" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U01-1</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="14" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="D3" s="14" t="inlineStr">
+        <is>
+          <t>这个周末我太忙了，一个电影___。</t>
+        </is>
+      </c>
+      <c r="E3" s="14" t="inlineStr">
+        <is>
+          <t>都没看</t>
+        </is>
+      </c>
+      <c r="F3" s="14" t="inlineStr">
+        <is>
+          <t>都很想看</t>
+        </is>
+      </c>
+      <c r="G3" s="14" t="inlineStr">
+        <is>
+          <t>都看了</t>
+        </is>
+      </c>
+      <c r="H3" s="14" t="inlineStr">
+        <is>
+          <t>也看完了</t>
+        </is>
+      </c>
+      <c r="I3" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J3" s="14" t="inlineStr">
+        <is>
+          <t>“一＋量词＋名词＋都/也”后面必须是否定，周末已经过去，所以用“都没看”。</t>
+        </is>
+      </c>
+      <c r="K3" s="14" t="inlineStr">
+        <is>
+          <t>一 + measure word + noun + 都/也 must be followed by a negative; the weekend is past, so 都没看.</t>
+        </is>
+      </c>
+      <c r="L3" s="14" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U01-1</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>找错</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>下面哪一句有错？</t>
+        </is>
+      </c>
+      <c r="E4" s="14" t="inlineStr">
+        <is>
+          <t>上个月他一次也不迟到过。</t>
+        </is>
+      </c>
+      <c r="F4" s="14" t="inlineStr">
+        <is>
+          <t>我对这个城市一点儿也不了解。</t>
+        </is>
+      </c>
+      <c r="G4" s="14" t="inlineStr">
+        <is>
+          <t>他一个字都没写。</t>
+        </is>
+      </c>
+      <c r="H4" s="14" t="inlineStr">
+        <is>
+          <t>这个问题我一点儿也不明白。</t>
+        </is>
+      </c>
+      <c r="I4" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J4" s="14" t="inlineStr">
+        <is>
+          <t>说过去的经历要用“没……过”，不能用“不”：上个月他一次也没迟到过。</t>
+        </is>
+      </c>
+      <c r="K4" s="14" t="inlineStr">
+        <is>
+          <t>For past experience use 没…过, not 不: 上个月他一次也没迟到过。</t>
+        </is>
+      </c>
+      <c r="L4" s="14" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U01-2</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>辨析</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>你的中文说得真好，你是在哪儿学___？</t>
+        </is>
+      </c>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>过</t>
+        </is>
+      </c>
+      <c r="F5" s="14" t="inlineStr">
+        <is>
+          <t>了</t>
+        </is>
+      </c>
+      <c r="G5" s="14" t="inlineStr">
+        <is>
+          <t>着</t>
+        </is>
+      </c>
+      <c r="H5" s="14" t="inlineStr">
+        <is>
+          <t>的</t>
+        </is>
+      </c>
+      <c r="I5" s="14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J5" s="14" t="inlineStr">
+        <is>
+          <t>“是……的”强调已经发生的动作的地点，句末要用“的”，不能用“了”。</t>
+        </is>
+      </c>
+      <c r="K5" s="14" t="inlineStr">
+        <is>
+          <t>是……的 stresses where a past action happened and must end with 的, not 了.</t>
+        </is>
+      </c>
+      <c r="L5" s="14" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U01-2</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>我是坐火车来北京的，___。</t>
+        </is>
+      </c>
+      <c r="E6" s="14" t="inlineStr">
+        <is>
+          <t>下个星期才能到</t>
+        </is>
+      </c>
+      <c r="F6" s="14" t="inlineStr">
+        <is>
+          <t>现在还在排队买票</t>
+        </is>
+      </c>
+      <c r="G6" s="14" t="inlineStr">
+        <is>
+          <t>路上只用了五个小时</t>
+        </is>
+      </c>
+      <c r="H6" s="14" t="inlineStr">
+        <is>
+          <t>票还没有买到呢</t>
+        </is>
+      </c>
+      <c r="I6" s="14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J6" s="14" t="inlineStr">
+        <is>
+          <t>“是……的”说的是已经发生的事，人已经到了北京，所以后面只能说路上的情况；“才能到、还在买票、还没买到”都表示还没来。</t>
+        </is>
+      </c>
+      <c r="K6" s="14" t="inlineStr">
+        <is>
+          <t>是…的 talks about something that has already happened: he is already in Beijing, so only a remark about the trip fits; the others mean he hasn't come yet.</t>
+        </is>
+      </c>
+      <c r="L6" s="14" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U01-2</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>找错</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>下面哪一句有错？</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>他是坐出租车来了的。</t>
+        </is>
+      </c>
+      <c r="F7" s="14" t="inlineStr">
+        <is>
+          <t>我是去年九月来中国的。</t>
+        </is>
+      </c>
+      <c r="G7" s="14" t="inlineStr">
+        <is>
+          <t>这件衣服是在网上买的。</t>
+        </is>
+      </c>
+      <c r="H7" s="14" t="inlineStr">
+        <is>
+          <t>你是跟谁一起去的？</t>
+        </is>
+      </c>
+      <c r="I7" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J7" s="14" t="inlineStr">
+        <is>
+          <t>“是……的”中间不能再用“了”：他是坐出租车来的。</t>
+        </is>
+      </c>
+      <c r="K7" s="14" t="inlineStr">
+        <is>
+          <t>No 了 inside 是……的: 他是坐出租车来的。</t>
+        </is>
+      </c>
+      <c r="L7" s="14" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U01-3</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>辨析</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>我在楼上等你，你快走___吧。</t>
+        </is>
+      </c>
+      <c r="E8" s="14" t="inlineStr">
+        <is>
+          <t>下来</t>
+        </is>
+      </c>
+      <c r="F8" s="14" t="inlineStr">
+        <is>
+          <t>上去</t>
+        </is>
+      </c>
+      <c r="G8" s="14" t="inlineStr">
+        <is>
+          <t>上来</t>
+        </is>
+      </c>
+      <c r="H8" s="14" t="inlineStr">
+        <is>
+          <t>进去</t>
+        </is>
+      </c>
+      <c r="I8" s="14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J8" s="14" t="inlineStr">
+        <is>
+          <t>说话人在楼上，对方要向上、向说话人走，所以用“上来”；“上去”是离开说话人。</t>
+        </is>
+      </c>
+      <c r="K8" s="14" t="inlineStr">
+        <is>
+          <t>The speaker is upstairs and the listener moves up toward him, so 上来; 上去 means moving away from the speaker.</t>
+        </is>
+      </c>
+      <c r="L8" s="14" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U01-3</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>我在___，听到朋友叫我，就跑下去了。</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>二楼的房间里</t>
+        </is>
+      </c>
+      <c r="F9" s="14" t="inlineStr">
+        <is>
+          <t>学校的门口</t>
+        </is>
+      </c>
+      <c r="G9" s="14" t="inlineStr">
+        <is>
+          <t>一楼的大门外</t>
+        </is>
+      </c>
+      <c r="H9" s="14" t="inlineStr">
+        <is>
+          <t>楼下的门口</t>
+        </is>
+      </c>
+      <c r="I9" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J9" s="14" t="inlineStr">
+        <is>
+          <t>“跑下去”是从高处往低处走，所以人原来应该在楼上。</t>
+        </is>
+      </c>
+      <c r="K9" s="14" t="inlineStr">
+        <is>
+          <t>跑下去 means running from a higher place to a lower one, so the person must have been upstairs.</t>
+        </is>
+      </c>
+      <c r="L9" s="14" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U01-3</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>找错</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>下面哪一句有错？</t>
+        </is>
+      </c>
+      <c r="E10" s="14" t="inlineStr">
+        <is>
+          <t>请把桌子上的书拿下来。</t>
+        </is>
+      </c>
+      <c r="F10" s="14" t="inlineStr">
+        <is>
+          <t>我下班以后就回家去。</t>
+        </is>
+      </c>
+      <c r="G10" s="14" t="inlineStr">
+        <is>
+          <t>他从外面走进来了。</t>
+        </is>
+      </c>
+      <c r="H10" s="14" t="inlineStr">
+        <is>
+          <t>老师走进去教室了。</t>
+        </is>
+      </c>
+      <c r="I10" s="14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J10" s="14" t="inlineStr">
+        <is>
+          <t>表示处所的宾语要放在“来/去”前面：老师走进教室去了（或：走进了教室）。</t>
+        </is>
+      </c>
+      <c r="K10" s="14" t="inlineStr">
+        <is>
+          <t>A place object goes before 来/去: 老师走进教室去了 (or 走进了教室).</t>
+        </is>
+      </c>
+      <c r="L10" s="14" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U01-4</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>辨析</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>连他最好的朋友___不知道这件事。</t>
+        </is>
+      </c>
+      <c r="E11" s="14" t="inlineStr">
+        <is>
+          <t>又</t>
+        </is>
+      </c>
+      <c r="F11" s="14" t="inlineStr">
+        <is>
+          <t>就</t>
+        </is>
+      </c>
+      <c r="G11" s="14" t="inlineStr">
+        <is>
+          <t>才</t>
+        </is>
+      </c>
+      <c r="H11" s="14" t="inlineStr">
+        <is>
+          <t>也</t>
+        </is>
+      </c>
+      <c r="I11" s="14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J11" s="14" t="inlineStr">
+        <is>
+          <t>“连”后面要用“也”或“都”来呼应，表示连最不可能的人都不知道；“又、就、才”不能这样用。</t>
+        </is>
+      </c>
+      <c r="K11" s="14" t="inlineStr">
+        <is>
+          <t>连 must be matched by 也 or 都 to mean 'even'; 又, 就 and 才 cannot pair with it.</t>
+        </is>
+      </c>
+      <c r="L11" s="14" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U01-4</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>这个汉字很常见，连___都认识。</t>
+        </is>
+      </c>
+      <c r="E12" s="14" t="inlineStr">
+        <is>
+          <t>研究汉字的教授</t>
+        </is>
+      </c>
+      <c r="F12" s="14" t="inlineStr">
+        <is>
+          <t>教中文的老师</t>
+        </is>
+      </c>
+      <c r="G12" s="14" t="inlineStr">
+        <is>
+          <t>中国的大学生</t>
+        </is>
+      </c>
+      <c r="H12" s="14" t="inlineStr">
+        <is>
+          <t>刚学中文的外国人</t>
+        </is>
+      </c>
+      <c r="I12" s="14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J12" s="14" t="inlineStr">
+        <is>
+          <t>“连”后面要放最不可能做到的人：连刚学中文的外国人都认识，才说明这个字常见；老师、专家认识很正常。</t>
+        </is>
+      </c>
+      <c r="K12" s="14" t="inlineStr">
+        <is>
+          <t>连 introduces the least likely case: if even beginners know it, the character is common; teachers or experts knowing it proves nothing.</t>
+        </is>
+      </c>
+      <c r="L12" s="14" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U01-4</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <t>找错</t>
+        </is>
+      </c>
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>下面哪一句有错？</t>
+        </is>
+      </c>
+      <c r="E13" s="14" t="inlineStr">
+        <is>
+          <t>连他妈妈都不知道他去哪儿了。</t>
+        </is>
+      </c>
+      <c r="F13" s="14" t="inlineStr">
+        <is>
+          <t>我连他的名字也忘了。</t>
+        </is>
+      </c>
+      <c r="G13" s="14" t="inlineStr">
+        <is>
+          <t>他连早饭没吃就走了。</t>
+        </is>
+      </c>
+      <c r="H13" s="14" t="inlineStr">
+        <is>
+          <t>他连一句谢谢都没说。</t>
+        </is>
+      </c>
+      <c r="I13" s="14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J13" s="14" t="inlineStr">
+        <is>
+          <t>“连”后面一定要有“都/也”：他连早饭都没吃就走了。</t>
+        </is>
+      </c>
+      <c r="K13" s="14" t="inlineStr">
+        <is>
+          <t>连 needs 都/也 after it: 他连早饭都没吃就走了.</t>
+        </is>
+      </c>
+      <c r="L13" s="14" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U02-1</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" s="14" t="inlineStr">
+        <is>
+          <t>辨析</t>
+        </is>
+      </c>
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>听说考试通过了，他高兴得___。</t>
+        </is>
+      </c>
+      <c r="E14" s="14" t="inlineStr">
+        <is>
+          <t>得了</t>
+        </is>
+      </c>
+      <c r="F14" s="14" t="inlineStr">
+        <is>
+          <t>了不起</t>
+        </is>
+      </c>
+      <c r="G14" s="14" t="inlineStr">
+        <is>
+          <t>不了</t>
+        </is>
+      </c>
+      <c r="H14" s="14" t="inlineStr">
+        <is>
+          <t>不得了</t>
+        </is>
+      </c>
+      <c r="I14" s="14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J14" s="14" t="inlineStr">
+        <is>
+          <t>“形容词＋得＋不得了”表示程度极高；“了不起”是夸人厉害，不能放在“得”后面作程度补语。</t>
+        </is>
+      </c>
+      <c r="K14" s="14" t="inlineStr">
+        <is>
+          <t>Adj + 得 + 不得了 means 'extremely'; 了不起 means 'amazing (person)' and is not a degree complement.</t>
+        </is>
+      </c>
+      <c r="L14" s="14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U02-1</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" s="14" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="D15" s="14" t="inlineStr">
+        <is>
+          <t>这家店的菜贵得不得了，___。</t>
+        </is>
+      </c>
+      <c r="E15" s="14" t="inlineStr">
+        <is>
+          <t>只比别的店贵一点儿</t>
+        </is>
+      </c>
+      <c r="F15" s="14" t="inlineStr">
+        <is>
+          <t>一个菜就要好几百块</t>
+        </is>
+      </c>
+      <c r="G15" s="14" t="inlineStr">
+        <is>
+          <t>比我想的稍微贵一些</t>
+        </is>
+      </c>
+      <c r="H15" s="14" t="inlineStr">
+        <is>
+          <t>跟附近的店比还算正常</t>
+        </is>
+      </c>
+      <c r="I15" s="14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J15" s="14" t="inlineStr">
+        <is>
+          <t>“贵得不得了”是非常非常贵，后面要说贵得很厉害的情况，不能说“贵一点儿、稍微贵”。</t>
+        </is>
+      </c>
+      <c r="K15" s="14" t="inlineStr">
+        <is>
+          <t>贵得不得了 means extremely expensive, so what follows must be very expensive, not just a little more.</t>
+        </is>
+      </c>
+      <c r="L15" s="14" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U02-1</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C16" s="14" t="inlineStr">
+        <is>
+          <t>找错</t>
+        </is>
+      </c>
+      <c r="D16" s="14" t="inlineStr">
+        <is>
+          <t>下面哪一句有错？</t>
+        </is>
+      </c>
+      <c r="E16" s="14" t="inlineStr">
+        <is>
+          <t>这里的风景不得了漂亮。</t>
+        </is>
+      </c>
+      <c r="F16" s="14" t="inlineStr">
+        <is>
+          <t>这个消息让大家高兴得不得了。</t>
+        </is>
+      </c>
+      <c r="G16" s="14" t="inlineStr">
+        <is>
+          <t>这个孩子聪明得不得了。</t>
+        </is>
+      </c>
+      <c r="H16" s="14" t="inlineStr">
+        <is>
+          <t>今天的作业多得不得了。</t>
+        </is>
+      </c>
+      <c r="I16" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J16" s="14" t="inlineStr">
+        <is>
+          <t>“不得了”要放在“形容词＋得”后面：这里的风景漂亮得不得了。</t>
+        </is>
+      </c>
+      <c r="K16" s="14" t="inlineStr">
+        <is>
+          <t>不得了 comes after adj + 得: 这里的风景漂亮得不得了.</t>
+        </is>
+      </c>
+      <c r="L16" s="14" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U02-2</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <t>辨析</t>
+        </is>
+      </c>
+      <c r="D17" s="14" t="inlineStr">
+        <is>
+          <t>他上周迟到了两次，今天___迟到了。</t>
+        </is>
+      </c>
+      <c r="E17" s="14" t="inlineStr">
+        <is>
+          <t>再</t>
+        </is>
+      </c>
+      <c r="F17" s="14" t="inlineStr">
+        <is>
+          <t>还要</t>
+        </is>
+      </c>
+      <c r="G17" s="14" t="inlineStr">
+        <is>
+          <t>又</t>
+        </is>
+      </c>
+      <c r="H17" s="14" t="inlineStr">
+        <is>
+          <t>重新</t>
+        </is>
+      </c>
+      <c r="I17" s="14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J17" s="14" t="inlineStr">
+        <is>
+          <t>已经发生的重复用“又”；“再”用于还没发生的重复，“重新”是从头再做一次。</t>
+        </is>
+      </c>
+      <c r="K17" s="14" t="inlineStr">
+        <is>
+          <t>For a repeat that has already happened use 又; 再 is for repeats that haven't happened yet, and 重新 means redo from the start.</t>
+        </is>
+      </c>
+      <c r="L17" s="14" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U02-2</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C18" s="14" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="D18" s="14" t="inlineStr">
+        <is>
+          <t>你刚才说得太快了，请你再___。</t>
+        </is>
+      </c>
+      <c r="E18" s="14" t="inlineStr">
+        <is>
+          <t>说一遍</t>
+        </is>
+      </c>
+      <c r="F18" s="14" t="inlineStr">
+        <is>
+          <t>说过一遍</t>
+        </is>
+      </c>
+      <c r="G18" s="14" t="inlineStr">
+        <is>
+          <t>说过了</t>
+        </is>
+      </c>
+      <c r="H18" s="14" t="inlineStr">
+        <is>
+          <t>说了一遍</t>
+        </is>
+      </c>
+      <c r="I18" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J18" s="14" t="inlineStr">
+        <is>
+          <t>“再”表示将来的重复，请求别人时后面不能带“了、过”。</t>
+        </is>
+      </c>
+      <c r="K18" s="14" t="inlineStr">
+        <is>
+          <t>再 is for a future repeat; in a request it cannot take 了 or 过.</t>
+        </is>
+      </c>
+      <c r="L18" s="14" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U02-2</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C19" s="14" t="inlineStr">
+        <is>
+          <t>找错</t>
+        </is>
+      </c>
+      <c r="D19" s="14" t="inlineStr">
+        <is>
+          <t>下面哪一句有错？</t>
+        </is>
+      </c>
+      <c r="E19" s="14" t="inlineStr">
+        <is>
+          <t>我昨天再去了一次那家书店。</t>
+        </is>
+      </c>
+      <c r="F19" s="14" t="inlineStr">
+        <is>
+          <t>这个问题我们明天再讨论吧。</t>
+        </is>
+      </c>
+      <c r="G19" s="14" t="inlineStr">
+        <is>
+          <t>这个菜很好吃，我明天还想再来吃。</t>
+        </is>
+      </c>
+      <c r="H19" s="14" t="inlineStr">
+        <is>
+          <t>她上个月病了一次，这个月又病了。</t>
+        </is>
+      </c>
+      <c r="I19" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J19" s="14" t="inlineStr">
+        <is>
+          <t>昨天已经发生的重复要用“又”：我昨天又去了一次那家书店。</t>
+        </is>
+      </c>
+      <c r="K19" s="14" t="inlineStr">
+        <is>
+          <t>A repeat that already happened yesterday needs 又: 我昨天又去了一次那家书店。</t>
+        </is>
+      </c>
+      <c r="L19" s="14" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U02-3</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C20" s="14" t="inlineStr">
+        <is>
+          <t>辨析</t>
+        </is>
+      </c>
+      <c r="D20" s="14" t="inlineStr">
+        <is>
+          <t>这件衣服有点儿大，有没有小___的？</t>
+        </is>
+      </c>
+      <c r="E20" s="14" t="inlineStr">
+        <is>
+          <t>有点儿</t>
+        </is>
+      </c>
+      <c r="F20" s="14" t="inlineStr">
+        <is>
+          <t>一下</t>
+        </is>
+      </c>
+      <c r="G20" s="14" t="inlineStr">
+        <is>
+          <t>一点儿</t>
+        </is>
+      </c>
+      <c r="H20" s="14" t="inlineStr">
+        <is>
+          <t>一会儿</t>
+        </is>
+      </c>
+      <c r="I20" s="14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J20" s="14" t="inlineStr">
+        <is>
+          <t>形容词后面表示比较、稍微用“一点儿”；“一下”放在动词后，“有点儿”放在形容词前。</t>
+        </is>
+      </c>
+      <c r="K20" s="14" t="inlineStr">
+        <is>
+          <t>After an adjective, 'a bit more' is 一点儿; 一下 follows verbs and 有点儿 goes before adjectives.</t>
+        </is>
+      </c>
+      <c r="L20" s="14" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U02-3</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C21" s="14" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="D21" s="14" t="inlineStr">
+        <is>
+          <t>天太冷了，我想喝一点儿___。</t>
+        </is>
+      </c>
+      <c r="E21" s="14" t="inlineStr">
+        <is>
+          <t>几碗热汤</t>
+        </is>
+      </c>
+      <c r="F21" s="14" t="inlineStr">
+        <is>
+          <t>一碗热汤</t>
+        </is>
+      </c>
+      <c r="G21" s="14" t="inlineStr">
+        <is>
+          <t>热汤</t>
+        </is>
+      </c>
+      <c r="H21" s="14" t="inlineStr">
+        <is>
+          <t>很多热汤</t>
+        </is>
+      </c>
+      <c r="I21" s="14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J21" s="14" t="inlineStr">
+        <is>
+          <t>“一点儿”后面直接加名词，不能再加“一碗、几碗、很多”这样的数量。</t>
+        </is>
+      </c>
+      <c r="K21" s="14" t="inlineStr">
+        <is>
+          <t>一点儿 is followed directly by the noun, with no extra amount like 一碗 or 很多.</t>
+        </is>
+      </c>
+      <c r="L21" s="14" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U02-3</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C22" s="14" t="inlineStr">
+        <is>
+          <t>找错</t>
+        </is>
+      </c>
+      <c r="D22" s="14" t="inlineStr">
+        <is>
+          <t>下面哪一句有错？</t>
+        </is>
+      </c>
+      <c r="E22" s="14" t="inlineStr">
+        <is>
+          <t>你能走快一点儿吗？</t>
+        </is>
+      </c>
+      <c r="F22" s="14" t="inlineStr">
+        <is>
+          <t>我想去超市买一点儿水果。</t>
+        </is>
+      </c>
+      <c r="G22" s="14" t="inlineStr">
+        <is>
+          <t>请你在这儿等一下。</t>
+        </is>
+      </c>
+      <c r="H22" s="14" t="inlineStr">
+        <is>
+          <t>今天一点儿冷，你多穿件衣服。</t>
+        </is>
+      </c>
+      <c r="I22" s="14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J22" s="14" t="inlineStr">
+        <is>
+          <t>形容词前面表示“有些不如意”要用“有点儿”：今天有点儿冷。</t>
+        </is>
+      </c>
+      <c r="K22" s="14" t="inlineStr">
+        <is>
+          <t>Before an adjective, 'a bit (too)' is 有点儿: 今天有点儿冷.</t>
+        </is>
+      </c>
+      <c r="L22" s="14" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U02-4</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C23" s="14" t="inlineStr">
+        <is>
+          <t>辨析</t>
+        </is>
+      </c>
+      <c r="D23" s="14" t="inlineStr">
+        <is>
+          <t>听了他的笑话，大家都笑___了。</t>
+        </is>
+      </c>
+      <c r="E23" s="14" t="inlineStr">
+        <is>
+          <t>下来</t>
+        </is>
+      </c>
+      <c r="F23" s="14" t="inlineStr">
+        <is>
+          <t>起来</t>
+        </is>
+      </c>
+      <c r="G23" s="14" t="inlineStr">
+        <is>
+          <t>下去</t>
+        </is>
+      </c>
+      <c r="H23" s="14" t="inlineStr">
+        <is>
+          <t>上来</t>
+        </is>
+      </c>
+      <c r="I23" s="14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J23" s="14" t="inlineStr">
+        <is>
+          <t>“起来”表示动作开始，“笑起来”就是开始笑；“下来、下去、上来”没有这个意思。</t>
+        </is>
+      </c>
+      <c r="K23" s="14" t="inlineStr">
+        <is>
+          <t>起来 marks the start of an action, so 笑起来 = start laughing; 下来, 下去 and 上来 do not mean that.</t>
+        </is>
+      </c>
+      <c r="L23" s="14" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U02-4</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C24" s="14" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="D24" s="14" t="inlineStr">
+        <is>
+          <t>说着说着，她___起来。</t>
+        </is>
+      </c>
+      <c r="E24" s="14" t="inlineStr">
+        <is>
+          <t>哭过</t>
+        </is>
+      </c>
+      <c r="F24" s="14" t="inlineStr">
+        <is>
+          <t>在哭</t>
+        </is>
+      </c>
+      <c r="G24" s="14" t="inlineStr">
+        <is>
+          <t>哭了</t>
+        </is>
+      </c>
+      <c r="H24" s="14" t="inlineStr">
+        <is>
+          <t>哭着</t>
+        </is>
+      </c>
+      <c r="I24" s="14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J24" s="14" t="inlineStr">
+        <is>
+          <t>表示开始的“起来”前面用动词或“动词＋了”，不能用“过、着、在”。</t>
+        </is>
+      </c>
+      <c r="K24" s="14" t="inlineStr">
+        <is>
+          <t>起来 (start) follows a bare verb or verb + 了, not 过, 着 or 在.</t>
+        </is>
+      </c>
+      <c r="L24" s="14" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U02-4</t>
+        </is>
+      </c>
+      <c r="B25" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C25" s="14" t="inlineStr">
+        <is>
+          <t>找错</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="inlineStr">
+        <is>
+          <t>下面哪一句有错？</t>
+        </is>
+      </c>
+      <c r="E25" s="14" t="inlineStr">
+        <is>
+          <t>他一回家就玩游戏起来。</t>
+        </is>
+      </c>
+      <c r="F25" s="14" t="inlineStr">
+        <is>
+          <t>孩子们高兴地唱起歌来。</t>
+        </is>
+      </c>
+      <c r="G25" s="14" t="inlineStr">
+        <is>
+          <t>最近他的身体好起来了。</t>
+        </is>
+      </c>
+      <c r="H25" s="14" t="inlineStr">
+        <is>
+          <t>他们一见面就聊起天来。</t>
+        </is>
+      </c>
+      <c r="I25" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J25" s="14" t="inlineStr">
+        <is>
+          <t>带宾语时宾语放在“起”和“来”中间：他一回家就玩起游戏来。</t>
+        </is>
+      </c>
+      <c r="K25" s="14" t="inlineStr">
+        <is>
+          <t>With an object, it goes between 起 and 来: 他一回家就玩起游戏来.</t>
+        </is>
+      </c>
+      <c r="L25" s="14" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U03-1</t>
+        </is>
+      </c>
+      <c r="B26" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C26" s="14" t="inlineStr">
+        <is>
+          <t>辨析</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="inlineStr">
+        <is>
+          <t>我们下周去上海，___住哪儿，到了再说。</t>
+        </is>
+      </c>
+      <c r="E26" s="14" t="inlineStr">
+        <is>
+          <t>至于</t>
+        </is>
+      </c>
+      <c r="F26" s="14" t="inlineStr">
+        <is>
+          <t>由于</t>
+        </is>
+      </c>
+      <c r="G26" s="14" t="inlineStr">
+        <is>
+          <t>至少</t>
+        </is>
+      </c>
+      <c r="H26" s="14" t="inlineStr">
+        <is>
+          <t>甚至</t>
+        </is>
+      </c>
+      <c r="I26" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J26" s="14" t="inlineStr">
+        <is>
+          <t>说完一件事再引出新话题用“至于”；“由于”表示原因，“甚至”表示更进一步。</t>
+        </is>
+      </c>
+      <c r="K26" s="14" t="inlineStr">
+        <is>
+          <t>至于 brings up a new topic; 由于 gives a reason and 甚至 means "even".</t>
+        </is>
+      </c>
+      <c r="L26" s="14" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U03-1</t>
+        </is>
+      </c>
+      <c r="B27" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C27" s="14" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="D27" s="14" t="inlineStr">
+        <is>
+          <t>这份工作工资不错，离家也近，至于___，我还要再问问。</t>
+        </is>
+      </c>
+      <c r="E27" s="14" t="inlineStr">
+        <is>
+          <t>工资高不高</t>
+        </is>
+      </c>
+      <c r="F27" s="14" t="inlineStr">
+        <is>
+          <t>离家远不远</t>
+        </is>
+      </c>
+      <c r="G27" s="14" t="inlineStr">
+        <is>
+          <t>上班近不近</t>
+        </is>
+      </c>
+      <c r="H27" s="14" t="inlineStr">
+        <is>
+          <t>每周休息几天</t>
+        </is>
+      </c>
+      <c r="I27" s="14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J27" s="14" t="inlineStr">
+        <is>
+          <t>“至于”要引出一个新话题；工资和远近前面已经说了，只有休息时间是新话题。</t>
+        </is>
+      </c>
+      <c r="K27" s="14" t="inlineStr">
+        <is>
+          <t>至于 introduces a new topic; pay and distance were already mentioned, only the days off are new.</t>
+        </is>
+      </c>
+      <c r="L27" s="14" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U03-1</t>
+        </is>
+      </c>
+      <c r="B28" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C28" s="14" t="inlineStr">
+        <is>
+          <t>找错</t>
+        </is>
+      </c>
+      <c r="D28" s="14" t="inlineStr">
+        <is>
+          <t>下面哪一句有错？</t>
+        </is>
+      </c>
+      <c r="E28" s="14" t="inlineStr">
+        <is>
+          <t>他会来，至于什么时候来，我不清楚。</t>
+        </is>
+      </c>
+      <c r="F28" s="14" t="inlineStr">
+        <is>
+          <t>他每天工作到很晚，至于身体越来越不好。</t>
+        </is>
+      </c>
+      <c r="G28" s="14" t="inlineStr">
+        <is>
+          <t>机票已经买好了，至于住的地方，还没找。</t>
+        </is>
+      </c>
+      <c r="H28" s="14" t="inlineStr">
+        <is>
+          <t>我喜欢这个城市，至于这里的冬天，我还不太习惯。</t>
+        </is>
+      </c>
+      <c r="I28" s="14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J28" s="14" t="inlineStr">
+        <is>
+          <t>这里要表示结果，应该用“以至于”或“所以”：他每天工作到很晚，以至于身体越来越不好。</t>
+        </is>
+      </c>
+      <c r="K28" s="14" t="inlineStr">
+        <is>
+          <t>A result is meant here, so use 以至于 or 所以 instead of 至于.</t>
+        </is>
+      </c>
+      <c r="L28" s="14" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U03-2</t>
+        </is>
+      </c>
+      <c r="B29" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C29" s="14" t="inlineStr">
+        <is>
+          <t>辨析</t>
+        </is>
+      </c>
+      <c r="D29" s="14" t="inlineStr">
+        <is>
+          <t>在家看电影太没意思了，___去电影院看。</t>
+        </is>
+      </c>
+      <c r="E29" s="14" t="inlineStr">
+        <is>
+          <t>没有</t>
+        </is>
+      </c>
+      <c r="F29" s="14" t="inlineStr">
+        <is>
+          <t>比</t>
+        </is>
+      </c>
+      <c r="G29" s="14" t="inlineStr">
+        <is>
+          <t>不如</t>
+        </is>
+      </c>
+      <c r="H29" s="14" t="inlineStr">
+        <is>
+          <t>跟</t>
+        </is>
+      </c>
+      <c r="I29" s="14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J29" s="14" t="inlineStr">
+        <is>
+          <t>“不如”可以单独用，表示“还是……更好”；“比、跟”后面必须有比较的结果。</t>
+        </is>
+      </c>
+      <c r="K29" s="14" t="inlineStr">
+        <is>
+          <t>不如 can stand alone meaning 'it would be better to'; 比 and 跟 need a result after them.</t>
+        </is>
+      </c>
+      <c r="L29" s="14" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U03-2</t>
+        </is>
+      </c>
+      <c r="B30" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C30" s="14" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="D30" s="14" t="inlineStr">
+        <is>
+          <t>这家饭馆的菜不如那家___。</t>
+        </is>
+      </c>
+      <c r="E30" s="14" t="inlineStr">
+        <is>
+          <t>难吃</t>
+        </is>
+      </c>
+      <c r="F30" s="14" t="inlineStr">
+        <is>
+          <t>差</t>
+        </is>
+      </c>
+      <c r="G30" s="14" t="inlineStr">
+        <is>
+          <t>一样</t>
+        </is>
+      </c>
+      <c r="H30" s="14" t="inlineStr">
+        <is>
+          <t>好吃</t>
+        </is>
+      </c>
+      <c r="I30" s="14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J30" s="14" t="inlineStr">
+        <is>
+          <t>“A不如B”后面一般用正面的形容词，意思是A没有B好吃；不能用“难吃、差”。</t>
+        </is>
+      </c>
+      <c r="K30" s="14" t="inlineStr">
+        <is>
+          <t>A 不如 B takes a positive adjective (A is not as tasty as B), not 难吃 or 差.</t>
+        </is>
+      </c>
+      <c r="L30" s="14" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U03-2</t>
+        </is>
+      </c>
+      <c r="B31" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C31" s="14" t="inlineStr">
+        <is>
+          <t>找错</t>
+        </is>
+      </c>
+      <c r="D31" s="14" t="inlineStr">
+        <is>
+          <t>下面哪一句有错？</t>
+        </is>
+      </c>
+      <c r="E31" s="14" t="inlineStr">
+        <is>
+          <t>一个人去不如大家一起去。</t>
+        </is>
+      </c>
+      <c r="F31" s="14" t="inlineStr">
+        <is>
+          <t>这个办法不如那个好。</t>
+        </is>
+      </c>
+      <c r="G31" s="14" t="inlineStr">
+        <is>
+          <t>我的房间不如他的房间脏。</t>
+        </is>
+      </c>
+      <c r="H31" s="14" t="inlineStr">
+        <is>
+          <t>这儿的天气不如南方暖和。</t>
+        </is>
+      </c>
+      <c r="I31" s="14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J31" s="14" t="inlineStr">
+        <is>
+          <t>“不如”后面不用负面形容词，可以说：我的房间没有他的房间脏。</t>
+        </is>
+      </c>
+      <c r="K31" s="14" t="inlineStr">
+        <is>
+          <t>不如 is not used with negative adjectives; say 我的房间没有他的房间脏.</t>
+        </is>
+      </c>
+      <c r="L31" s="14" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U03-3</t>
+        </is>
+      </c>
+      <c r="B32" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C32" s="14" t="inlineStr">
+        <is>
+          <t>辨析</t>
+        </is>
+      </c>
+      <c r="D32" s="14" t="inlineStr">
+        <is>
+          <t>我们班二十个学生，男生五个，是全班的___。</t>
+        </is>
+      </c>
+      <c r="E32" s="14" t="inlineStr">
+        <is>
+          <t>五分之一</t>
+        </is>
+      </c>
+      <c r="F32" s="14" t="inlineStr">
+        <is>
+          <t>四分之一</t>
+        </is>
+      </c>
+      <c r="G32" s="14" t="inlineStr">
+        <is>
+          <t>一分之四</t>
+        </is>
+      </c>
+      <c r="H32" s="14" t="inlineStr">
+        <is>
+          <t>百分之五</t>
+        </is>
+      </c>
+      <c r="I32" s="14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J32" s="14" t="inlineStr">
+        <is>
+          <t>分数先说分母再说分子，二十个里有五个就是“四分之一”；“一分之四”顺序反了。</t>
+        </is>
+      </c>
+      <c r="K32" s="14" t="inlineStr">
+        <is>
+          <t>Say the denominator first: 5 out of 20 is 四分之一; 一分之四 has the order reversed.</t>
+        </is>
+      </c>
+      <c r="L32" s="14" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U03-3</t>
+        </is>
+      </c>
+      <c r="B33" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C33" s="14" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="D33" s="14" t="inlineStr">
+        <is>
+          <t>全班三分之一是女生，就是说___。</t>
+        </is>
+      </c>
+      <c r="E33" s="14" t="inlineStr">
+        <is>
+          <t>三个人里有一个女生</t>
+        </is>
+      </c>
+      <c r="F33" s="14" t="inlineStr">
+        <is>
+          <t>三个人里有两个女生</t>
+        </is>
+      </c>
+      <c r="G33" s="14" t="inlineStr">
+        <is>
+          <t>男生女生一样多</t>
+        </is>
+      </c>
+      <c r="H33" s="14" t="inlineStr">
+        <is>
+          <t>男生是女生的三倍</t>
+        </is>
+      </c>
+      <c r="I33" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J33" s="14" t="inlineStr">
+        <is>
+          <t>“三分之一”是分成三份占一份，就是三个人里有一个女生。</t>
+        </is>
+      </c>
+      <c r="K33" s="14" t="inlineStr">
+        <is>
+          <t>三分之一 is one of three parts, so one in every three students is a girl.</t>
+        </is>
+      </c>
+      <c r="L33" s="14" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U03-3</t>
+        </is>
+      </c>
+      <c r="B34" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C34" s="14" t="inlineStr">
+        <is>
+          <t>找错</t>
+        </is>
+      </c>
+      <c r="D34" s="14" t="inlineStr">
+        <is>
+          <t>下面哪一句有错？</t>
+        </is>
+      </c>
+      <c r="E34" s="14" t="inlineStr">
+        <is>
+          <t>我们班百分五十的学生是女生。</t>
+        </is>
+      </c>
+      <c r="F34" s="14" t="inlineStr">
+        <is>
+          <t>我们只完成了五分之一的工作。</t>
+        </is>
+      </c>
+      <c r="G34" s="14" t="inlineStr">
+        <is>
+          <t>他把工资的百分之二十存了起来。</t>
+        </is>
+      </c>
+      <c r="H34" s="14" t="inlineStr">
+        <is>
+          <t>三分之二的人同意这个办法。</t>
+        </is>
+      </c>
+      <c r="I34" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J34" s="14" t="inlineStr">
+        <is>
+          <t>百分数中间不能少“之”：百分之五十的学生是女生。</t>
+        </is>
+      </c>
+      <c r="K34" s="14" t="inlineStr">
+        <is>
+          <t>A percentage needs 之: 百分之五十.</t>
+        </is>
+      </c>
+      <c r="L34" s="14" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U03-4</t>
+        </is>
+      </c>
+      <c r="B35" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C35" s="14" t="inlineStr">
+        <is>
+          <t>辨析</t>
+        </is>
+      </c>
+      <c r="D35" s="14" t="inlineStr">
+        <is>
+          <t>这家饭馆的菜___可以，不过不算特别好吃。</t>
+        </is>
+      </c>
+      <c r="E35" s="14" t="inlineStr">
+        <is>
+          <t>更</t>
+        </is>
+      </c>
+      <c r="F35" s="14" t="inlineStr">
+        <is>
+          <t>最</t>
+        </is>
+      </c>
+      <c r="G35" s="14" t="inlineStr">
+        <is>
+          <t>还</t>
+        </is>
+      </c>
+      <c r="H35" s="14" t="inlineStr">
+        <is>
+          <t>太</t>
+        </is>
+      </c>
+      <c r="I35" s="14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J35" s="14" t="inlineStr">
+        <is>
+          <t>“还＋可以”表示马马虎虎、过得去，正好跟后面的“不算特别好吃”配合。</t>
+        </is>
+      </c>
+      <c r="K35" s="14" t="inlineStr">
+        <is>
+          <t>还 + 可以 means 'passable', which matches 'not especially tasty'.</t>
+        </is>
+      </c>
+      <c r="L35" s="14" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U03-4</t>
+        </is>
+      </c>
+      <c r="B36" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C36" s="14" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="D36" s="14" t="inlineStr">
+        <is>
+          <t>你的汉字写得还可以，___。</t>
+        </is>
+      </c>
+      <c r="E36" s="14" t="inlineStr">
+        <is>
+          <t>是全班写得最好的</t>
+        </is>
+      </c>
+      <c r="F36" s="14" t="inlineStr">
+        <is>
+          <t>就是有的字写得太小</t>
+        </is>
+      </c>
+      <c r="G36" s="14" t="inlineStr">
+        <is>
+          <t>大家都说漂亮极了</t>
+        </is>
+      </c>
+      <c r="H36" s="14" t="inlineStr">
+        <is>
+          <t>比老师写得还漂亮</t>
+        </is>
+      </c>
+      <c r="I36" s="14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J36" s="14" t="inlineStr">
+        <is>
+          <t>“还可以”是不错但不是很好，后面常说一点不足，不能接很高的评价。</t>
+        </is>
+      </c>
+      <c r="K36" s="14" t="inlineStr">
+        <is>
+          <t>还可以 means OK but not great, so a small weakness follows, not high praise.</t>
+        </is>
+      </c>
+      <c r="L36" s="14" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U03-4</t>
+        </is>
+      </c>
+      <c r="B37" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C37" s="14" t="inlineStr">
+        <is>
+          <t>找错</t>
+        </is>
+      </c>
+      <c r="D37" s="14" t="inlineStr">
+        <is>
+          <t>下面哪一句有错？</t>
+        </is>
+      </c>
+      <c r="E37" s="14" t="inlineStr">
+        <is>
+          <t>这个电影还好极了，我看了三遍。</t>
+        </is>
+      </c>
+      <c r="F37" s="14" t="inlineStr">
+        <is>
+          <t>今天的天气还可以。</t>
+        </is>
+      </c>
+      <c r="G37" s="14" t="inlineStr">
+        <is>
+          <t>这个办法还行。</t>
+        </is>
+      </c>
+      <c r="H37" s="14" t="inlineStr">
+        <is>
+          <t>这个房间还挺干净的。</t>
+        </is>
+      </c>
+      <c r="I37" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J37" s="14" t="inlineStr">
+        <is>
+          <t>“还”表示一般、过得去，不能跟“极了”一起用：这个电影好极了。</t>
+        </is>
+      </c>
+      <c r="K37" s="14" t="inlineStr">
+        <is>
+          <t>还 means 'fairly OK' and cannot go with 极了; say 这个电影好极了.</t>
+        </is>
+      </c>
+      <c r="L37" s="14" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U04-1</t>
+        </is>
+      </c>
+      <c r="B38" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="C38" s="14" t="inlineStr">
+        <is>
+          <t>辨析</t>
+        </is>
+      </c>
+      <c r="D38" s="14" t="inlineStr">
+        <is>
+          <t>我们是去年认识的，到现在只___。</t>
+        </is>
+      </c>
+      <c r="E38" s="14" t="inlineStr">
+        <is>
+          <t>见面过两次</t>
+        </is>
+      </c>
+      <c r="F38" s="14" t="inlineStr">
+        <is>
+          <t>见过两次面</t>
+        </is>
+      </c>
+      <c r="G38" s="14" t="inlineStr">
+        <is>
+          <t>见过面两次</t>
+        </is>
+      </c>
+      <c r="H38" s="14" t="inlineStr">
+        <is>
+          <t>两次见过面</t>
+        </is>
+      </c>
+      <c r="I38" s="14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J38" s="14" t="inlineStr">
+        <is>
+          <t>“见面”是离合词，“过”和次数要插在“见”和“面”中间。</t>
+        </is>
+      </c>
+      <c r="K38" s="14" t="inlineStr">
+        <is>
+          <t>见面 is a separable verb: 过 and the count go between 见 and 面.</t>
+        </is>
+      </c>
+      <c r="L38" s="14" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U04-1</t>
+        </is>
+      </c>
+      <c r="B39" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="C39" s="14" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="D39" s="14" t="inlineStr">
+        <is>
+          <t>昨天晚上我睡了___觉，今天一点儿也不累。</t>
+        </is>
+      </c>
+      <c r="E39" s="14" t="inlineStr">
+        <is>
+          <t>很多</t>
+        </is>
+      </c>
+      <c r="F39" s="14" t="inlineStr">
+        <is>
+          <t>一个好</t>
+        </is>
+      </c>
+      <c r="G39" s="14" t="inlineStr">
+        <is>
+          <t>一点儿</t>
+        </is>
+      </c>
+      <c r="H39" s="14" t="inlineStr">
+        <is>
+          <t>很好</t>
+        </is>
+      </c>
+      <c r="I39" s="14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J39" s="14" t="inlineStr">
+        <is>
+          <t>离合词中间可以加“一个好”这样的数量修饰，“很好、很多”不能插在中间。</t>
+        </is>
+      </c>
+      <c r="K39" s="14" t="inlineStr">
+        <is>
+          <t>A separable verb can take 一个好 in the middle; 很好 and 很多 cannot go there.</t>
+        </is>
+      </c>
+      <c r="L39" s="14" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U04-1</t>
+        </is>
+      </c>
+      <c r="B40" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="C40" s="14" t="inlineStr">
+        <is>
+          <t>找错</t>
+        </is>
+      </c>
+      <c r="D40" s="14" t="inlineStr">
+        <is>
+          <t>下面哪一句有错？</t>
+        </is>
+      </c>
+      <c r="E40" s="14" t="inlineStr">
+        <is>
+          <t>他帮了我很多忙。</t>
+        </is>
+      </c>
+      <c r="F40" s="14" t="inlineStr">
+        <is>
+          <t>他昨天游了一个小时泳。</t>
+        </is>
+      </c>
+      <c r="G40" s="14" t="inlineStr">
+        <is>
+          <t>我们聊了一会儿天。</t>
+        </is>
+      </c>
+      <c r="H40" s="14" t="inlineStr">
+        <is>
+          <t>我昨天见面了我的老朋友。</t>
+        </is>
+      </c>
+      <c r="I40" s="14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J40" s="14" t="inlineStr">
+        <is>
+          <t>“见面”后面不能再带宾语，应说：我昨天跟我的老朋友见面了。</t>
+        </is>
+      </c>
+      <c r="K40" s="14" t="inlineStr">
+        <is>
+          <t>见面 cannot take an object; say 我昨天跟我的老朋友见面了.</t>
+        </is>
+      </c>
+      <c r="L40" s="14" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U04-2</t>
+        </is>
+      </c>
+      <c r="B41" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="C41" s="14" t="inlineStr">
+        <is>
+          <t>辨析</t>
+        </is>
+      </c>
+      <c r="D41" s="14" t="inlineStr">
+        <is>
+          <t>我是___网上的广告找到这份工作的。</t>
+        </is>
+      </c>
+      <c r="E41" s="14" t="inlineStr">
+        <is>
+          <t>关于</t>
+        </is>
+      </c>
+      <c r="F41" s="14" t="inlineStr">
+        <is>
+          <t>对于</t>
+        </is>
+      </c>
+      <c r="G41" s="14" t="inlineStr">
+        <is>
+          <t>经过</t>
+        </is>
+      </c>
+      <c r="H41" s="14" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="I41" s="14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J41" s="14" t="inlineStr">
+        <is>
+          <t>“通过”引出做事的方法或途径；“经过”多指时间、过程或路过某地。</t>
+        </is>
+      </c>
+      <c r="K41" s="14" t="inlineStr">
+        <is>
+          <t>通过 introduces a means or channel; 经过 is about a process, time, or passing a place.</t>
+        </is>
+      </c>
+      <c r="L41" s="14" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U04-2</t>
+        </is>
+      </c>
+      <c r="B42" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="C42" s="14" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="D42" s="14" t="inlineStr">
+        <is>
+          <t>通过这次实习，___。</t>
+        </is>
+      </c>
+      <c r="E42" s="14" t="inlineStr">
+        <is>
+          <t>我每天都要坐地铁上班</t>
+        </is>
+      </c>
+      <c r="F42" s="14" t="inlineStr">
+        <is>
+          <t>我实习的公司在市中心</t>
+        </is>
+      </c>
+      <c r="G42" s="14" t="inlineStr">
+        <is>
+          <t>我对这份工作了解多了</t>
+        </is>
+      </c>
+      <c r="H42" s="14" t="inlineStr">
+        <is>
+          <t>我下个月就开始实习</t>
+        </is>
+      </c>
+      <c r="I42" s="14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J42" s="14" t="inlineStr">
+        <is>
+          <t>“通过……”说的是经过某种方法或经历得到的结果，实习以后对工作更了解了；上下班的方式、公司在哪儿都不是实习带来的结果，下个月才开始也跟“这次实习”矛盾。</t>
+        </is>
+      </c>
+      <c r="K42" s="14" t="inlineStr">
+        <is>
+          <t>通过… states a result gained through a means or experience: after the internship I know the job better; how I commute or where the company is are not results of it.</t>
+        </is>
+      </c>
+      <c r="L42" s="14" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U04-2</t>
+        </is>
+      </c>
+      <c r="B43" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="C43" s="14" t="inlineStr">
+        <is>
+          <t>找错</t>
+        </is>
+      </c>
+      <c r="D43" s="14" t="inlineStr">
+        <is>
+          <t>下面哪一句有错？</t>
+        </is>
+      </c>
+      <c r="E43" s="14" t="inlineStr">
+        <is>
+          <t>我们可以通过电话联系。</t>
+        </is>
+      </c>
+      <c r="F43" s="14" t="inlineStr">
+        <is>
+          <t>他通过朋友找到了房子。</t>
+        </is>
+      </c>
+      <c r="G43" s="14" t="inlineStr">
+        <is>
+          <t>通过这次旅行，我更了解中国了。</t>
+        </is>
+      </c>
+      <c r="H43" s="14" t="inlineStr">
+        <is>
+          <t>我每天上班都通过那家书店。</t>
+        </is>
+      </c>
+      <c r="I43" s="14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J43" s="14" t="inlineStr">
+        <is>
+          <t>路过某个地方要用“经过”：我每天上班都经过那家书店。</t>
+        </is>
+      </c>
+      <c r="K43" s="14" t="inlineStr">
+        <is>
+          <t>For passing by a place use 经过: 我每天上班都经过那家书店。</t>
+        </is>
+      </c>
+      <c r="L43" s="14" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U04-3</t>
+        </is>
+      </c>
+      <c r="B44" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="C44" s="14" t="inlineStr">
+        <is>
+          <t>辨析</t>
+        </is>
+      </c>
+      <c r="D44" s="14" t="inlineStr">
+        <is>
+          <t>这次会议___李经理主持。</t>
+        </is>
+      </c>
+      <c r="E44" s="14" t="inlineStr">
+        <is>
+          <t>由</t>
+        </is>
+      </c>
+      <c r="F44" s="14" t="inlineStr">
+        <is>
+          <t>被</t>
+        </is>
+      </c>
+      <c r="G44" s="14" t="inlineStr">
+        <is>
+          <t>对</t>
+        </is>
+      </c>
+      <c r="H44" s="14" t="inlineStr">
+        <is>
+          <t>从</t>
+        </is>
+      </c>
+      <c r="I44" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J44" s="14" t="inlineStr">
+        <is>
+          <t>“由”引出负责做这件事的人；“被”多用于不如意的事，这里不合适。</t>
+        </is>
+      </c>
+      <c r="K44" s="14" t="inlineStr">
+        <is>
+          <t>由 introduces who is responsible for doing it; 被 is mostly for unwanted events and does not fit here.</t>
+        </is>
+      </c>
+      <c r="L44" s="14" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U04-3</t>
+        </is>
+      </c>
+      <c r="B45" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="C45" s="14" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="D45" s="14" t="inlineStr">
+        <is>
+          <t>这次晚会的节目由学生们___。</t>
+        </is>
+      </c>
+      <c r="E45" s="14" t="inlineStr">
+        <is>
+          <t>觉得不错</t>
+        </is>
+      </c>
+      <c r="F45" s="14" t="inlineStr">
+        <is>
+          <t>自己准备</t>
+        </is>
+      </c>
+      <c r="G45" s="14" t="inlineStr">
+        <is>
+          <t>都很喜欢</t>
+        </is>
+      </c>
+      <c r="H45" s="14" t="inlineStr">
+        <is>
+          <t>非常高兴</t>
+        </is>
+      </c>
+      <c r="I45" s="14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J45" s="14" t="inlineStr">
+        <is>
+          <t>“由”后面的人要负责去做一件事，所以要跟“准备”这样的动作。</t>
+        </is>
+      </c>
+      <c r="K45" s="14" t="inlineStr">
+        <is>
+          <t>With 由, the person carries out a task, so an action like 准备 must follow.</t>
+        </is>
+      </c>
+      <c r="L45" s="14" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U04-3</t>
+        </is>
+      </c>
+      <c r="B46" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="C46" s="14" t="inlineStr">
+        <is>
+          <t>找错</t>
+        </is>
+      </c>
+      <c r="D46" s="14" t="inlineStr">
+        <is>
+          <t>下面哪一句有错？</t>
+        </is>
+      </c>
+      <c r="E46" s="14" t="inlineStr">
+        <is>
+          <t>我的蛋糕由弟弟吃了。</t>
+        </is>
+      </c>
+      <c r="F46" s="14" t="inlineStr">
+        <is>
+          <t>学生的作业由老师检查。</t>
+        </is>
+      </c>
+      <c r="G46" s="14" t="inlineStr">
+        <is>
+          <t>这次比赛由王老师来安排。</t>
+        </is>
+      </c>
+      <c r="H46" s="14" t="inlineStr">
+        <is>
+          <t>孩子们的午饭由学校提供。</t>
+        </is>
+      </c>
+      <c r="I46" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J46" s="14" t="inlineStr">
+        <is>
+          <t>蛋糕被吃掉是不如意的事，不是谁“负责”做的事，要用“被”：我的蛋糕被弟弟吃了。</t>
+        </is>
+      </c>
+      <c r="K46" s="14" t="inlineStr">
+        <is>
+          <t>Having your cake eaten is not a task someone is in charge of; use 被: 我的蛋糕被弟弟吃了.</t>
+        </is>
+      </c>
+      <c r="L46" s="14" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U04-4</t>
+        </is>
+      </c>
+      <c r="B47" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="C47" s="14" t="inlineStr">
+        <is>
+          <t>辨析</t>
+        </is>
+      </c>
+      <c r="D47" s="14" t="inlineStr">
+        <is>
+          <t>请___周一前交作业。</t>
+        </is>
+      </c>
+      <c r="E47" s="14" t="inlineStr">
+        <is>
+          <t>由于</t>
+        </is>
+      </c>
+      <c r="F47" s="14" t="inlineStr">
+        <is>
+          <t>对于</t>
+        </is>
+      </c>
+      <c r="G47" s="14" t="inlineStr">
+        <is>
+          <t>于</t>
+        </is>
+      </c>
+      <c r="H47" s="14" t="inlineStr">
+        <is>
+          <t>在于</t>
+        </is>
+      </c>
+      <c r="I47" s="14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J47" s="14" t="inlineStr">
+        <is>
+          <t>书面语里“于”相当于“在”，“于周一前”就是“在周一前”。</t>
+        </is>
+      </c>
+      <c r="K47" s="14" t="inlineStr">
+        <is>
+          <t>In written Chinese 于 means 在, so 于周一前 = before Monday.</t>
+        </is>
+      </c>
+      <c r="L47" s="14" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U04-4</t>
+        </is>
+      </c>
+      <c r="B48" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="C48" s="14" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="D48" s="14" t="inlineStr">
+        <is>
+          <t>如需帮助，___。</t>
+        </is>
+      </c>
+      <c r="E48" s="14" t="inlineStr">
+        <is>
+          <t>请给我们打电话</t>
+        </is>
+      </c>
+      <c r="F48" s="14" t="inlineStr">
+        <is>
+          <t>例如学习和工作上的问题</t>
+        </is>
+      </c>
+      <c r="G48" s="14" t="inlineStr">
+        <is>
+          <t>像这样的帮助很多</t>
+        </is>
+      </c>
+      <c r="H48" s="14" t="inlineStr">
+        <is>
+          <t>比如说找房子</t>
+        </is>
+      </c>
+      <c r="I48" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J48" s="14" t="inlineStr">
+        <is>
+          <t>书面语“如”就是“如果”，后面要说在这个条件下怎么做；它不是“比如、像”的意思。</t>
+        </is>
+      </c>
+      <c r="K48" s="14" t="inlineStr">
+        <is>
+          <t>In formal writing 如 means "if", so the next part says what to do; it does not mean "for example".</t>
+        </is>
+      </c>
+      <c r="L48" s="14" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U04-4</t>
+        </is>
+      </c>
+      <c r="B49" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="C49" s="14" t="inlineStr">
+        <is>
+          <t>找错</t>
+        </is>
+      </c>
+      <c r="D49" s="14" t="inlineStr">
+        <is>
+          <t>下面哪一句有错？</t>
+        </is>
+      </c>
+      <c r="E49" s="14" t="inlineStr">
+        <is>
+          <t>请于下午五点前离开教室。</t>
+        </is>
+      </c>
+      <c r="F49" s="14" t="inlineStr">
+        <is>
+          <t>请通过电话或邮件报名。</t>
+        </is>
+      </c>
+      <c r="G49" s="14" t="inlineStr">
+        <is>
+          <t>这家公司成立于在2005年。</t>
+        </is>
+      </c>
+      <c r="H49" s="14" t="inlineStr">
+        <is>
+          <t>如有问题，请与我们联系。</t>
+        </is>
+      </c>
+      <c r="I49" s="14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J49" s="14" t="inlineStr">
+        <is>
+          <t>“于”就是“在”的意思，“于在”重复了，应说“这家公司成立于2005年”。</t>
+        </is>
+      </c>
+      <c r="K49" s="14" t="inlineStr">
+        <is>
+          <t>于 already means 在, so 于在 is doubled; say 这家公司成立于2005年.</t>
+        </is>
+      </c>
+      <c r="L49" s="14" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U05-1</t>
+        </is>
+      </c>
+      <c r="B50" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C50" s="14" t="inlineStr">
+        <is>
+          <t>辨析</t>
+        </is>
+      </c>
+      <c r="D50" s="14" t="inlineStr">
+        <is>
+          <t>这个房子不大，房间___挺多的。</t>
+        </is>
+      </c>
+      <c r="E50" s="14" t="inlineStr">
+        <is>
+          <t>就</t>
+        </is>
+      </c>
+      <c r="F50" s="14" t="inlineStr">
+        <is>
+          <t>都</t>
+        </is>
+      </c>
+      <c r="G50" s="14" t="inlineStr">
+        <is>
+          <t>倒</t>
+        </is>
+      </c>
+      <c r="H50" s="14" t="inlineStr">
+        <is>
+          <t>才</t>
+        </is>
+      </c>
+      <c r="I50" s="14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J50" s="14" t="inlineStr">
+        <is>
+          <t>“倒”表示跟前面的情况相反，房子不大却房间多。</t>
+        </is>
+      </c>
+      <c r="K50" s="14" t="inlineStr">
+        <is>
+          <t>倒 marks a contrast with what came before: the flat is small, yet it has many rooms.</t>
+        </is>
+      </c>
+      <c r="L50" s="14" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U05-1</t>
+        </is>
+      </c>
+      <c r="B51" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C51" s="14" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="D51" s="14" t="inlineStr">
+        <is>
+          <t>这家饭馆环境一般，菜倒___。</t>
+        </is>
+      </c>
+      <c r="E51" s="14" t="inlineStr">
+        <is>
+          <t>很难吃</t>
+        </is>
+      </c>
+      <c r="F51" s="14" t="inlineStr">
+        <is>
+          <t>也一般</t>
+        </is>
+      </c>
+      <c r="G51" s="14" t="inlineStr">
+        <is>
+          <t>挺好吃</t>
+        </is>
+      </c>
+      <c r="H51" s="14" t="inlineStr">
+        <is>
+          <t>不太好吃</t>
+        </is>
+      </c>
+      <c r="I51" s="14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J51" s="14" t="inlineStr">
+        <is>
+          <t>“倒”表示跟前面相反：环境一般，菜却挺好吃。</t>
+        </is>
+      </c>
+      <c r="K51" s="14" t="inlineStr">
+        <is>
+          <t>倒 marks a contrast with what came before: the setting is ordinary, but the food is actually good.</t>
+        </is>
+      </c>
+      <c r="L51" s="14" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U05-1</t>
+        </is>
+      </c>
+      <c r="B52" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C52" s="14" t="inlineStr">
+        <is>
+          <t>找错</t>
+        </is>
+      </c>
+      <c r="D52" s="14" t="inlineStr">
+        <is>
+          <t>下面哪一句有错？</t>
+        </is>
+      </c>
+      <c r="E52" s="14" t="inlineStr">
+        <is>
+          <t>他学中文时间不长，说得倒挺流利。</t>
+        </is>
+      </c>
+      <c r="F52" s="14" t="inlineStr">
+        <is>
+          <t>这里冬天很冷，夏天倒挺舒服。</t>
+        </is>
+      </c>
+      <c r="G52" s="14" t="inlineStr">
+        <is>
+          <t>他个子不高，篮球倒打得很好。</t>
+        </is>
+      </c>
+      <c r="H52" s="14" t="inlineStr">
+        <is>
+          <t>这个手机很便宜，倒质量很好。</t>
+        </is>
+      </c>
+      <c r="I52" s="14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J52" s="14" t="inlineStr">
+        <is>
+          <t>“倒”是副词，要放在主语后面：这个手机很便宜，质量倒很好。</t>
+        </is>
+      </c>
+      <c r="K52" s="14" t="inlineStr">
+        <is>
+          <t>倒 is an adverb and goes after the subject: 质量倒很好.</t>
+        </is>
+      </c>
+      <c r="L52" s="14" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U05-2</t>
+        </is>
+      </c>
+      <c r="B53" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C53" s="14" t="inlineStr">
+        <is>
+          <t>辨析</t>
+        </is>
+      </c>
+      <c r="D53" s="14" t="inlineStr">
+        <is>
+          <t>考试快到了，你得___复习一下。</t>
+        </is>
+      </c>
+      <c r="E53" s="14" t="inlineStr">
+        <is>
+          <t>好好</t>
+        </is>
+      </c>
+      <c r="F53" s="14" t="inlineStr">
+        <is>
+          <t>很好</t>
+        </is>
+      </c>
+      <c r="G53" s="14" t="inlineStr">
+        <is>
+          <t>好极了</t>
+        </is>
+      </c>
+      <c r="H53" s="14" t="inlineStr">
+        <is>
+          <t>挺好</t>
+        </is>
+      </c>
+      <c r="I53" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J53" s="14" t="inlineStr">
+        <is>
+          <t>“好好＋动词”表示认真地做；“很好、挺好、好极了”是评价，不能直接放在动词前面。</t>
+        </is>
+      </c>
+      <c r="K53" s="14" t="inlineStr">
+        <is>
+          <t>好好 + verb means "do it properly"; 很好/挺好/好极了 are judgments and can't go right before a verb.</t>
+        </is>
+      </c>
+      <c r="L53" s="14" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U05-2</t>
+        </is>
+      </c>
+      <c r="B54" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C54" s="14" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="D54" s="14" t="inlineStr">
+        <is>
+          <t>你这几天太累了，周末好好___吧。</t>
+        </is>
+      </c>
+      <c r="E54" s="14" t="inlineStr">
+        <is>
+          <t>休息着</t>
+        </is>
+      </c>
+      <c r="F54" s="14" t="inlineStr">
+        <is>
+          <t>休息休息</t>
+        </is>
+      </c>
+      <c r="G54" s="14" t="inlineStr">
+        <is>
+          <t>休息过</t>
+        </is>
+      </c>
+      <c r="H54" s="14" t="inlineStr">
+        <is>
+          <t>休息了</t>
+        </is>
+      </c>
+      <c r="I54" s="14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J54" s="14" t="inlineStr">
+        <is>
+          <t>“好好”用来建议、要求，后面常跟动词或动词重叠，不能带“过、了、着”。</t>
+        </is>
+      </c>
+      <c r="K54" s="14" t="inlineStr">
+        <is>
+          <t>好好 in a suggestion takes a verb or doubled verb, not 过, 了 or 着.</t>
+        </is>
+      </c>
+      <c r="L54" s="14" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U05-2</t>
+        </is>
+      </c>
+      <c r="B55" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C55" s="14" t="inlineStr">
+        <is>
+          <t>找错</t>
+        </is>
+      </c>
+      <c r="D55" s="14" t="inlineStr">
+        <is>
+          <t>下面哪一句有错？</t>
+        </is>
+      </c>
+      <c r="E55" s="14" t="inlineStr">
+        <is>
+          <t>他汉语说得好好。</t>
+        </is>
+      </c>
+      <c r="F55" s="14" t="inlineStr">
+        <is>
+          <t>这次旅行我想好好玩一玩。</t>
+        </is>
+      </c>
+      <c r="G55" s="14" t="inlineStr">
+        <is>
+          <t>我们好好想一想再决定。</t>
+        </is>
+      </c>
+      <c r="H55" s="14" t="inlineStr">
+        <is>
+          <t>你要好好照顾自己。</t>
+        </is>
+      </c>
+      <c r="I55" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J55" s="14" t="inlineStr">
+        <is>
+          <t>“好好”放在动词前，不能作“得”后的补语：他汉语说得很好。</t>
+        </is>
+      </c>
+      <c r="K55" s="14" t="inlineStr">
+        <is>
+          <t>好好 goes before verbs, not after 得; say 他汉语说得很好.</t>
+        </is>
+      </c>
+      <c r="L55" s="14" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U05-3</t>
+        </is>
+      </c>
+      <c r="B56" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C56" s="14" t="inlineStr">
+        <is>
+          <t>辨析</t>
+        </is>
+      </c>
+      <c r="D56" s="14" t="inlineStr">
+        <is>
+          <t>___你已经决定了，我就不说什么了。</t>
+        </is>
+      </c>
+      <c r="E56" s="14" t="inlineStr">
+        <is>
+          <t>既然</t>
+        </is>
+      </c>
+      <c r="F56" s="14" t="inlineStr">
+        <is>
+          <t>即使</t>
+        </is>
+      </c>
+      <c r="G56" s="14" t="inlineStr">
+        <is>
+          <t>虽然</t>
+        </is>
+      </c>
+      <c r="H56" s="14" t="inlineStr">
+        <is>
+          <t>尽管</t>
+        </is>
+      </c>
+      <c r="I56" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J56" s="14" t="inlineStr">
+        <is>
+          <t>“既然”引出已知的事实，后面用“就”得出结论；“虽然、尽管、即使”不跟“就”这样配合。</t>
+        </is>
+      </c>
+      <c r="K56" s="14" t="inlineStr">
+        <is>
+          <t>既然 gives a known fact and 就 draws the conclusion; 虽然, 尽管 and 即使 do not pair with 就 here.</t>
+        </is>
+      </c>
+      <c r="L56" s="14" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U05-3</t>
+        </is>
+      </c>
+      <c r="B57" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C57" s="14" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="D57" s="14" t="inlineStr">
+        <is>
+          <t>既然这件衣服你穿着不合适，___。</t>
+        </is>
+      </c>
+      <c r="E57" s="14" t="inlineStr">
+        <is>
+          <t>虽然很好看</t>
+        </is>
+      </c>
+      <c r="F57" s="14" t="inlineStr">
+        <is>
+          <t>但是可以买</t>
+        </is>
+      </c>
+      <c r="G57" s="14" t="inlineStr">
+        <is>
+          <t>可是很便宜</t>
+        </is>
+      </c>
+      <c r="H57" s="14" t="inlineStr">
+        <is>
+          <t>那就换一件吧</t>
+        </is>
+      </c>
+      <c r="I57" s="14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J57" s="14" t="inlineStr">
+        <is>
+          <t>“既然”说出已知事实，后面用“就”得出结论；“但是、可是、虽然”表示转折，不能跟“既然”配合。</t>
+        </is>
+      </c>
+      <c r="K57" s="14" t="inlineStr">
+        <is>
+          <t>既然 states a known fact and leads to a conclusion with 就; 但是/可是/虽然 show contrast and don't pair with it.</t>
+        </is>
+      </c>
+      <c r="L57" s="14" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U05-3</t>
+        </is>
+      </c>
+      <c r="B58" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C58" s="14" t="inlineStr">
+        <is>
+          <t>找错</t>
+        </is>
+      </c>
+      <c r="D58" s="14" t="inlineStr">
+        <is>
+          <t>下面哪一句有错？</t>
+        </is>
+      </c>
+      <c r="E58" s="14" t="inlineStr">
+        <is>
+          <t>既然大家都同意，那就这么办吧。</t>
+        </is>
+      </c>
+      <c r="F58" s="14" t="inlineStr">
+        <is>
+          <t>既然你很忙，但是你还是来了。</t>
+        </is>
+      </c>
+      <c r="G58" s="14" t="inlineStr">
+        <is>
+          <t>既然来了，就多住几天吧。</t>
+        </is>
+      </c>
+      <c r="H58" s="14" t="inlineStr">
+        <is>
+          <t>既然你不舒服，就早点儿回家吧。</t>
+        </is>
+      </c>
+      <c r="I58" s="14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J58" s="14" t="inlineStr">
+        <is>
+          <t>表示转折应该用“虽然……但是……”：虽然你很忙，但是你还是来了。</t>
+        </is>
+      </c>
+      <c r="K58" s="14" t="inlineStr">
+        <is>
+          <t>For a contrast use 虽然……但是……, not 既然.</t>
+        </is>
+      </c>
+      <c r="L58" s="14" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U05-4</t>
+        </is>
+      </c>
+      <c r="B59" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C59" s="14" t="inlineStr">
+        <is>
+          <t>辨析</t>
+        </is>
+      </c>
+      <c r="D59" s="14" t="inlineStr">
+        <is>
+          <t>你能来帮忙，那___好不过了。</t>
+        </is>
+      </c>
+      <c r="E59" s="14" t="inlineStr">
+        <is>
+          <t>最</t>
+        </is>
+      </c>
+      <c r="F59" s="14" t="inlineStr">
+        <is>
+          <t>很</t>
+        </is>
+      </c>
+      <c r="G59" s="14" t="inlineStr">
+        <is>
+          <t>再</t>
+        </is>
+      </c>
+      <c r="H59" s="14" t="inlineStr">
+        <is>
+          <t>更</t>
+        </is>
+      </c>
+      <c r="I59" s="14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J59" s="14" t="inlineStr">
+        <is>
+          <t>固定格式是“再＋形容词＋不过了”，表示没有比这更……的了。</t>
+        </is>
+      </c>
+      <c r="K59" s="14" t="inlineStr">
+        <is>
+          <t>The fixed pattern is 再 + adj + 不过了, meaning nothing could be more so.</t>
+        </is>
+      </c>
+      <c r="L59" s="14" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U05-4</t>
+        </is>
+      </c>
+      <c r="B60" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C60" s="14" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="D60" s="14" t="inlineStr">
+        <is>
+          <t>这家店离地铁站只有一分钟，交通再___不过了。</t>
+        </is>
+      </c>
+      <c r="E60" s="14" t="inlineStr">
+        <is>
+          <t>方便</t>
+        </is>
+      </c>
+      <c r="F60" s="14" t="inlineStr">
+        <is>
+          <t>不方便</t>
+        </is>
+      </c>
+      <c r="G60" s="14" t="inlineStr">
+        <is>
+          <t>很方便</t>
+        </is>
+      </c>
+      <c r="H60" s="14" t="inlineStr">
+        <is>
+          <t>方便了</t>
+        </is>
+      </c>
+      <c r="I60" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J60" s="14" t="inlineStr">
+        <is>
+          <t>“再……不过了”中间放一个光杆形容词，不能加“很、了”，意思也要跟前面一致。</t>
+        </is>
+      </c>
+      <c r="K60" s="14" t="inlineStr">
+        <is>
+          <t>再……不过了 takes a bare adjective, without 很 or 了, matching the context.</t>
+        </is>
+      </c>
+      <c r="L60" s="14" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U05-4</t>
+        </is>
+      </c>
+      <c r="B61" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C61" s="14" t="inlineStr">
+        <is>
+          <t>找错</t>
+        </is>
+      </c>
+      <c r="D61" s="14" t="inlineStr">
+        <is>
+          <t>下面哪一句有错？</t>
+        </is>
+      </c>
+      <c r="E61" s="14" t="inlineStr">
+        <is>
+          <t>这件事交给他办再合适不过了。</t>
+        </is>
+      </c>
+      <c r="F61" s="14" t="inlineStr">
+        <is>
+          <t>这个菜再好吃了不过。</t>
+        </is>
+      </c>
+      <c r="G61" s="14" t="inlineStr">
+        <is>
+          <t>能和大家一起工作，我再高兴不过了。</t>
+        </is>
+      </c>
+      <c r="H61" s="14" t="inlineStr">
+        <is>
+          <t>这个问题再简单不过了。</t>
+        </is>
+      </c>
+      <c r="I61" s="14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J61" s="14" t="inlineStr">
+        <is>
+          <t>“了”要放在最后：这个菜再好吃不过了。</t>
+        </is>
+      </c>
+      <c r="K61" s="14" t="inlineStr">
+        <is>
+          <t>了 must come last: 这个菜再好吃不过了.</t>
+        </is>
+      </c>
+      <c r="L61" s="14" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U06-1</t>
+        </is>
+      </c>
+      <c r="B62" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="C62" s="14" t="inlineStr">
+        <is>
+          <t>辨析</t>
+        </is>
+      </c>
+      <c r="D62" s="14" t="inlineStr">
+        <is>
+          <t>一天没吃东西，我饿___。</t>
+        </is>
+      </c>
+      <c r="E62" s="14" t="inlineStr">
+        <is>
+          <t>死得很</t>
+        </is>
+      </c>
+      <c r="F62" s="14" t="inlineStr">
+        <is>
+          <t>得死了</t>
+        </is>
+      </c>
+      <c r="G62" s="14" t="inlineStr">
+        <is>
+          <t>死了</t>
+        </is>
+      </c>
+      <c r="H62" s="14" t="inlineStr">
+        <is>
+          <t>得死</t>
+        </is>
+      </c>
+      <c r="I62" s="14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J62" s="14" t="inlineStr">
+        <is>
+          <t>表示程度极高直接说“形容词＋死了”，中间不加“得”。</t>
+        </is>
+      </c>
+      <c r="K62" s="14" t="inlineStr">
+        <is>
+          <t>Extreme degree is adj + 死了 directly, with no 得.</t>
+        </is>
+      </c>
+      <c r="L62" s="14" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U06-1</t>
+        </is>
+      </c>
+      <c r="B63" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="C63" s="14" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="D63" s="14" t="inlineStr">
+        <is>
+          <t>听说他考上了北京大学，他妈妈___死了。</t>
+        </is>
+      </c>
+      <c r="E63" s="14" t="inlineStr">
+        <is>
+          <t>高兴</t>
+        </is>
+      </c>
+      <c r="F63" s="14" t="inlineStr">
+        <is>
+          <t>高兴得</t>
+        </is>
+      </c>
+      <c r="G63" s="14" t="inlineStr">
+        <is>
+          <t>很高兴</t>
+        </is>
+      </c>
+      <c r="H63" s="14" t="inlineStr">
+        <is>
+          <t>非常高兴</t>
+        </is>
+      </c>
+      <c r="I63" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J63" s="14" t="inlineStr">
+        <is>
+          <t>“死了”已经表示程度极高，前面不能再加“很、非常”，也不加“得”。</t>
+        </is>
+      </c>
+      <c r="K63" s="14" t="inlineStr">
+        <is>
+          <t>死了 already means 'extremely', so no 很, 非常 or 得 before it.</t>
+        </is>
+      </c>
+      <c r="L63" s="14" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U06-1</t>
+        </is>
+      </c>
+      <c r="B64" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="C64" s="14" t="inlineStr">
+        <is>
+          <t>找错</t>
+        </is>
+      </c>
+      <c r="D64" s="14" t="inlineStr">
+        <is>
+          <t>下面哪一句有错？</t>
+        </is>
+      </c>
+      <c r="E64" s="14" t="inlineStr">
+        <is>
+          <t>外面冷死了，快进来吧。</t>
+        </is>
+      </c>
+      <c r="F64" s="14" t="inlineStr">
+        <is>
+          <t>这个电影非常好看死了。</t>
+        </is>
+      </c>
+      <c r="G64" s="14" t="inlineStr">
+        <is>
+          <t>我今天忙死了。</t>
+        </is>
+      </c>
+      <c r="H64" s="14" t="inlineStr">
+        <is>
+          <t>这个消息把我急死了。</t>
+        </is>
+      </c>
+      <c r="I64" s="14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J64" s="14" t="inlineStr">
+        <is>
+          <t>“死了”前面不能再用“非常”：这个电影好看死了。</t>
+        </is>
+      </c>
+      <c r="K64" s="14" t="inlineStr">
+        <is>
+          <t>No 非常 before ……死了; say 这个电影好看死了.</t>
+        </is>
+      </c>
+      <c r="L64" s="14" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U06-2</t>
+        </is>
+      </c>
+      <c r="B65" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="C65" s="14" t="inlineStr">
+        <is>
+          <t>辨析</t>
+        </is>
+      </c>
+      <c r="D65" s="14" t="inlineStr">
+        <is>
+          <t>我的钱包丢了，___早点儿发现就好了。</t>
+        </is>
+      </c>
+      <c r="E65" s="14" t="inlineStr">
+        <is>
+          <t>即使</t>
+        </is>
+      </c>
+      <c r="F65" s="14" t="inlineStr">
+        <is>
+          <t>因为</t>
+        </is>
+      </c>
+      <c r="G65" s="14" t="inlineStr">
+        <is>
+          <t>虽然</t>
+        </is>
+      </c>
+      <c r="H65" s="14" t="inlineStr">
+        <is>
+          <t>要是</t>
+        </is>
+      </c>
+      <c r="I65" s="14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J65" s="14" t="inlineStr">
+        <is>
+          <t>“要是……就好了”表示希望或遗憾；“即使、虽然、因为”都不能跟“就好了”构成愿望。</t>
+        </is>
+      </c>
+      <c r="K65" s="14" t="inlineStr">
+        <is>
+          <t>要是……就好了 expresses a wish or regret; 即使, 虽然 and 因为 cannot form a wish with 就好了.</t>
+        </is>
+      </c>
+      <c r="L65" s="14" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U06-2</t>
+        </is>
+      </c>
+      <c r="B66" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="C66" s="14" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="D66" s="14" t="inlineStr">
+        <is>
+          <t>要是我会说中文就好了，___。</t>
+        </is>
+      </c>
+      <c r="E66" s="14" t="inlineStr">
+        <is>
+          <t>可惜我一句也不会</t>
+        </is>
+      </c>
+      <c r="F66" s="14" t="inlineStr">
+        <is>
+          <t>所以我常常跟中国人聊天</t>
+        </is>
+      </c>
+      <c r="G66" s="14" t="inlineStr">
+        <is>
+          <t>我已经说得很好了</t>
+        </is>
+      </c>
+      <c r="H66" s="14" t="inlineStr">
+        <is>
+          <t>我每天都用中文聊天</t>
+        </is>
+      </c>
+      <c r="I66" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J66" s="14" t="inlineStr">
+        <is>
+          <t>“要是……就好了”表示愿望，说的是现在还不是这样的情况，所以后面说“可惜我一句也不会”。</t>
+        </is>
+      </c>
+      <c r="K66" s="14" t="inlineStr">
+        <is>
+          <t>要是…就好了 is a wish about something not true now, so it goes on with "unfortunately I can't speak a word".</t>
+        </is>
+      </c>
+      <c r="L66" s="14" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U06-2</t>
+        </is>
+      </c>
+      <c r="B67" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="C67" s="14" t="inlineStr">
+        <is>
+          <t>找错</t>
+        </is>
+      </c>
+      <c r="D67" s="14" t="inlineStr">
+        <is>
+          <t>下面哪一句有错？</t>
+        </is>
+      </c>
+      <c r="E67" s="14" t="inlineStr">
+        <is>
+          <t>如果我能早点儿知道就好了。</t>
+        </is>
+      </c>
+      <c r="F67" s="14" t="inlineStr">
+        <is>
+          <t>要是我有时间就好了去旅游。</t>
+        </is>
+      </c>
+      <c r="G67" s="14" t="inlineStr">
+        <is>
+          <t>要是你也在这儿就好了。</t>
+        </is>
+      </c>
+      <c r="H67" s="14" t="inlineStr">
+        <is>
+          <t>要是今天不上班就好了。</t>
+        </is>
+      </c>
+      <c r="I67" s="14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J67" s="14" t="inlineStr">
+        <is>
+          <t>“就好了”要放在句子最后：要是我有时间去旅游就好了。</t>
+        </is>
+      </c>
+      <c r="K67" s="14" t="inlineStr">
+        <is>
+          <t>就好了 goes at the very end: 要是我有时间去旅游就好了.</t>
+        </is>
+      </c>
+      <c r="L67" s="14" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U06-3</t>
+        </is>
+      </c>
+      <c r="B68" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="C68" s="14" t="inlineStr">
+        <is>
+          <t>辨析</t>
+        </is>
+      </c>
+      <c r="D68" s="14" t="inlineStr">
+        <is>
+          <t>明天的考试很重要，你___别迟到啊！</t>
+        </is>
+      </c>
+      <c r="E68" s="14" t="inlineStr">
+        <is>
+          <t>倒</t>
+        </is>
+      </c>
+      <c r="F68" s="14" t="inlineStr">
+        <is>
+          <t>还</t>
+        </is>
+      </c>
+      <c r="G68" s="14" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="H68" s="14" t="inlineStr">
+        <is>
+          <t>才</t>
+        </is>
+      </c>
+      <c r="I68" s="14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J68" s="14" t="inlineStr">
+        <is>
+          <t>“可”加强语气，常用在“可别……”里提醒别人。</t>
+        </is>
+      </c>
+      <c r="K68" s="14" t="inlineStr">
+        <is>
+          <t>可 adds emphasis and is common in 可别…… warnings.</t>
+        </is>
+      </c>
+      <c r="L68" s="14" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U06-3</t>
+        </is>
+      </c>
+      <c r="B69" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="C69" s="14" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="D69" s="14" t="inlineStr">
+        <is>
+          <t>这个地方的菜可___了！</t>
+        </is>
+      </c>
+      <c r="E69" s="14" t="inlineStr">
+        <is>
+          <t>好吃的</t>
+        </is>
+      </c>
+      <c r="F69" s="14" t="inlineStr">
+        <is>
+          <t>好吃</t>
+        </is>
+      </c>
+      <c r="G69" s="14" t="inlineStr">
+        <is>
+          <t>好吃得很</t>
+        </is>
+      </c>
+      <c r="H69" s="14" t="inlineStr">
+        <is>
+          <t>很好吃</t>
+        </is>
+      </c>
+      <c r="I69" s="14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J69" s="14" t="inlineStr">
+        <is>
+          <t>“可＋形容词＋了”，中间只放形容词，不加“很”或补语。</t>
+        </is>
+      </c>
+      <c r="K69" s="14" t="inlineStr">
+        <is>
+          <t>可 + adj + 了 takes a bare adjective, no 很 or complement.</t>
+        </is>
+      </c>
+      <c r="L69" s="14" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U06-3</t>
+        </is>
+      </c>
+      <c r="B70" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="C70" s="14" t="inlineStr">
+        <is>
+          <t>找错</t>
+        </is>
+      </c>
+      <c r="D70" s="14" t="inlineStr">
+        <is>
+          <t>下面哪一句有错？</t>
+        </is>
+      </c>
+      <c r="E70" s="14" t="inlineStr">
+        <is>
+          <t>你可来了，我们等了你半天。</t>
+        </is>
+      </c>
+      <c r="F70" s="14" t="inlineStr">
+        <is>
+          <t>这件事你可别告诉他。</t>
+        </is>
+      </c>
+      <c r="G70" s="14" t="inlineStr">
+        <is>
+          <t>今天可热了。</t>
+        </is>
+      </c>
+      <c r="H70" s="14" t="inlineStr">
+        <is>
+          <t>他可很聪明了。</t>
+        </is>
+      </c>
+      <c r="I70" s="14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J70" s="14" t="inlineStr">
+        <is>
+          <t>“可”本身就加强程度，不能再加“很”：他可聪明了。</t>
+        </is>
+      </c>
+      <c r="K70" s="14" t="inlineStr">
+        <is>
+          <t>可 already intensifies, so drop 很: 他可聪明了.</t>
+        </is>
+      </c>
+      <c r="L70" s="14" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U06-4</t>
+        </is>
+      </c>
+      <c r="B71" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="C71" s="14" t="inlineStr">
+        <is>
+          <t>辨析</t>
+        </is>
+      </c>
+      <c r="D71" s="14" t="inlineStr">
+        <is>
+          <t>你别着急，___我们还有时间，慢慢来。</t>
+        </is>
+      </c>
+      <c r="E71" s="14" t="inlineStr">
+        <is>
+          <t>而且</t>
+        </is>
+      </c>
+      <c r="F71" s="14" t="inlineStr">
+        <is>
+          <t>不过</t>
+        </is>
+      </c>
+      <c r="G71" s="14" t="inlineStr">
+        <is>
+          <t>反而</t>
+        </is>
+      </c>
+      <c r="H71" s="14" t="inlineStr">
+        <is>
+          <t>反正</t>
+        </is>
+      </c>
+      <c r="I71" s="14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J71" s="14" t="inlineStr">
+        <is>
+          <t>“反正”给出理由，表示不管怎样情况都一样；“反而”表示跟预料相反。</t>
+        </is>
+      </c>
+      <c r="K71" s="14" t="inlineStr">
+        <is>
+          <t>反正 gives a reason that makes the rest not matter; 反而 means 'on the contrary'.</t>
+        </is>
+      </c>
+      <c r="L71" s="14" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U06-4</t>
+        </is>
+      </c>
+      <c r="B72" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="C72" s="14" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="D72" s="14" t="inlineStr">
+        <is>
+          <t>不管你同不同意，反正___。</t>
+        </is>
+      </c>
+      <c r="E72" s="14" t="inlineStr">
+        <is>
+          <t>由你来决定</t>
+        </is>
+      </c>
+      <c r="F72" s="14" t="inlineStr">
+        <is>
+          <t>我还没想好</t>
+        </is>
+      </c>
+      <c r="G72" s="14" t="inlineStr">
+        <is>
+          <t>我都听你的</t>
+        </is>
+      </c>
+      <c r="H72" s="14" t="inlineStr">
+        <is>
+          <t>我已经决定了</t>
+        </is>
+      </c>
+      <c r="I72" s="14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J72" s="14" t="inlineStr">
+        <is>
+          <t>“反正”表示不管情况怎样，结论都不变，所以是“我已经决定了”；“听你的、由你决定”跟“不管你同不同意”矛盾。</t>
+        </is>
+      </c>
+      <c r="K72" s="14" t="inlineStr">
+        <is>
+          <t>反正 means the conclusion stays the same whatever happens, so "I've already decided"; leaving it to you clashes with "whether you agree or not".</t>
+        </is>
+      </c>
+      <c r="L72" s="14" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U06-4</t>
+        </is>
+      </c>
+      <c r="B73" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="C73" s="14" t="inlineStr">
+        <is>
+          <t>找错</t>
+        </is>
+      </c>
+      <c r="D73" s="14" t="inlineStr">
+        <is>
+          <t>下面哪一句有错？</t>
+        </is>
+      </c>
+      <c r="E73" s="14" t="inlineStr">
+        <is>
+          <t>他学习很努力，反正成绩不太好。</t>
+        </is>
+      </c>
+      <c r="F73" s="14" t="inlineStr">
+        <is>
+          <t>你别买了，反正家里还有很多。</t>
+        </is>
+      </c>
+      <c r="G73" s="14" t="inlineStr">
+        <is>
+          <t>反正我也没事，就陪你去吧。</t>
+        </is>
+      </c>
+      <c r="H73" s="14" t="inlineStr">
+        <is>
+          <t>不管你怎么说，反正我不去。</t>
+        </is>
+      </c>
+      <c r="I73" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J73" s="14" t="inlineStr">
+        <is>
+          <t>这里是转折，不是理由，应该用“可是”：他学习很努力，可是成绩不太好。</t>
+        </is>
+      </c>
+      <c r="K73" s="14" t="inlineStr">
+        <is>
+          <t>This is a contrast, not a reason; use 可是 instead of 反正.</t>
+        </is>
+      </c>
+      <c r="L73" s="14" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U07-1</t>
+        </is>
+      </c>
+      <c r="B74" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="C74" s="14" t="inlineStr">
+        <is>
+          <t>辨析</t>
+        </is>
+      </c>
+      <c r="D74" s="14" t="inlineStr">
+        <is>
+          <t>都十点了，你___还不起床？</t>
+        </is>
+      </c>
+      <c r="E74" s="14" t="inlineStr">
+        <is>
+          <t>怎样</t>
+        </is>
+      </c>
+      <c r="F74" s="14" t="inlineStr">
+        <is>
+          <t>多么</t>
+        </is>
+      </c>
+      <c r="G74" s="14" t="inlineStr">
+        <is>
+          <t>怎么</t>
+        </is>
+      </c>
+      <c r="H74" s="14" t="inlineStr">
+        <is>
+          <t>怎么样</t>
+        </is>
+      </c>
+      <c r="I74" s="14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J74" s="14" t="inlineStr">
+        <is>
+          <t>“怎么”放在动词前表示奇怪、意外；“怎样、怎么样”问方式或情况，不能这样用。</t>
+        </is>
+      </c>
+      <c r="K74" s="14" t="inlineStr">
+        <is>
+          <t>怎么 before a verb shows surprise ("how come"); 怎样/怎么样 ask about manner or condition and can't be used here.</t>
+        </is>
+      </c>
+      <c r="L74" s="14" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U07-1</t>
+        </is>
+      </c>
+      <c r="B75" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="C75" s="14" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="D75" s="14" t="inlineStr">
+        <is>
+          <t>你怎么___？大家都在等你。</t>
+        </is>
+      </c>
+      <c r="E75" s="14" t="inlineStr">
+        <is>
+          <t>现在才来</t>
+        </is>
+      </c>
+      <c r="F75" s="14" t="inlineStr">
+        <is>
+          <t>来不来呢</t>
+        </is>
+      </c>
+      <c r="G75" s="14" t="inlineStr">
+        <is>
+          <t>已经来吗</t>
+        </is>
+      </c>
+      <c r="H75" s="14" t="inlineStr">
+        <is>
+          <t>一定来了</t>
+        </is>
+      </c>
+      <c r="I75" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J75" s="14" t="inlineStr">
+        <is>
+          <t>表示奇怪、不满的“怎么”问已经发生的事，比如“怎么现在才来”；不能跟“吗”或正反问一起用。</t>
+        </is>
+      </c>
+      <c r="K75" s="14" t="inlineStr">
+        <is>
+          <t>怎么 (how come) asks about something that has happened, e.g. 怎么现在才来; it can't take 吗 or an A-not-A question.</t>
+        </is>
+      </c>
+      <c r="L75" s="14" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U07-1</t>
+        </is>
+      </c>
+      <c r="B76" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="C76" s="14" t="inlineStr">
+        <is>
+          <t>找错</t>
+        </is>
+      </c>
+      <c r="D76" s="14" t="inlineStr">
+        <is>
+          <t>下面哪一句有错？</t>
+        </is>
+      </c>
+      <c r="E76" s="14" t="inlineStr">
+        <is>
+          <t>外面怎么这么吵？</t>
+        </is>
+      </c>
+      <c r="F76" s="14" t="inlineStr">
+        <is>
+          <t>你怎么不高兴了？</t>
+        </is>
+      </c>
+      <c r="G76" s="14" t="inlineStr">
+        <is>
+          <t>你怎么去了北京吗？</t>
+        </is>
+      </c>
+      <c r="H76" s="14" t="inlineStr">
+        <is>
+          <t>他怎么还没到呢？</t>
+        </is>
+      </c>
+      <c r="I76" s="14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J76" s="14" t="inlineStr">
+        <is>
+          <t>有了疑问词“怎么”，句末不能再用“吗”：你怎么去了北京？</t>
+        </is>
+      </c>
+      <c r="K76" s="14" t="inlineStr">
+        <is>
+          <t>With the question word 怎么, do not add 吗: 你怎么去了北京？</t>
+        </is>
+      </c>
+      <c r="L76" s="14" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U07-2</t>
+        </is>
+      </c>
+      <c r="B77" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="C77" s="14" t="inlineStr">
+        <is>
+          <t>辨析</t>
+        </is>
+      </c>
+      <c r="D77" s="14" t="inlineStr">
+        <is>
+          <t>你说了半天，___想不想去啊？</t>
+        </is>
+      </c>
+      <c r="E77" s="14" t="inlineStr">
+        <is>
+          <t>到底</t>
+        </is>
+      </c>
+      <c r="F77" s="14" t="inlineStr">
+        <is>
+          <t>最后</t>
+        </is>
+      </c>
+      <c r="G77" s="14" t="inlineStr">
+        <is>
+          <t>终于</t>
+        </is>
+      </c>
+      <c r="H77" s="14" t="inlineStr">
+        <is>
+          <t>已经</t>
+        </is>
+      </c>
+      <c r="I77" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J77" s="14" t="inlineStr">
+        <is>
+          <t>“到底”用在问句里加强追问；“终于、最后、已经”说的是事情的结果或状态，不能用来追问。</t>
+        </is>
+      </c>
+      <c r="K77" s="14" t="inlineStr">
+        <is>
+          <t>到底 presses for an answer in a question; 终于, 最后 and 已经 describe an outcome or state and cannot press a question.</t>
+        </is>
+      </c>
+      <c r="L77" s="14" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U07-2</t>
+        </is>
+      </c>
+      <c r="B78" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="C78" s="14" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="D78" s="14" t="inlineStr">
+        <is>
+          <t>这件事你到底___？</t>
+        </is>
+      </c>
+      <c r="E78" s="14" t="inlineStr">
+        <is>
+          <t>很同意</t>
+        </is>
+      </c>
+      <c r="F78" s="14" t="inlineStr">
+        <is>
+          <t>同意不同意</t>
+        </is>
+      </c>
+      <c r="G78" s="14" t="inlineStr">
+        <is>
+          <t>同意吗</t>
+        </is>
+      </c>
+      <c r="H78" s="14" t="inlineStr">
+        <is>
+          <t>同意了吧</t>
+        </is>
+      </c>
+      <c r="I78" s="14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J78" s="14" t="inlineStr">
+        <is>
+          <t>“到底”要跟正反问或疑问词一起用，不能跟“吗、吧”。</t>
+        </is>
+      </c>
+      <c r="K78" s="14" t="inlineStr">
+        <is>
+          <t>到底 goes with an A-not-A or question-word question, not 吗 or 吧.</t>
+        </is>
+      </c>
+      <c r="L78" s="14" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U07-2</t>
+        </is>
+      </c>
+      <c r="B79" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="C79" s="14" t="inlineStr">
+        <is>
+          <t>找错</t>
+        </is>
+      </c>
+      <c r="D79" s="14" t="inlineStr">
+        <is>
+          <t>下面哪一句有错？</t>
+        </is>
+      </c>
+      <c r="E79" s="14" t="inlineStr">
+        <is>
+          <t>你到底是学生吗？</t>
+        </is>
+      </c>
+      <c r="F79" s="14" t="inlineStr">
+        <is>
+          <t>这到底是谁的书？</t>
+        </is>
+      </c>
+      <c r="G79" s="14" t="inlineStr">
+        <is>
+          <t>你究竟想要什么？</t>
+        </is>
+      </c>
+      <c r="H79" s="14" t="inlineStr">
+        <is>
+          <t>这个包到底多少钱？</t>
+        </is>
+      </c>
+      <c r="I79" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J79" s="14" t="inlineStr">
+        <is>
+          <t>“到底”不跟“吗”一起用，应说：你到底是不是学生？</t>
+        </is>
+      </c>
+      <c r="K79" s="14" t="inlineStr">
+        <is>
+          <t>到底 does not go with 吗; say 你到底是不是学生？</t>
+        </is>
+      </c>
+      <c r="L79" s="14" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U07-3</t>
+        </is>
+      </c>
+      <c r="B80" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="C80" s="14" t="inlineStr">
+        <is>
+          <t>辨析</t>
+        </is>
+      </c>
+      <c r="D80" s="14" t="inlineStr">
+        <is>
+          <t>别担心，我___是有点儿累罢了。</t>
+        </is>
+      </c>
+      <c r="E80" s="14" t="inlineStr">
+        <is>
+          <t>还</t>
+        </is>
+      </c>
+      <c r="F80" s="14" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="G80" s="14" t="inlineStr">
+        <is>
+          <t>都</t>
+        </is>
+      </c>
+      <c r="H80" s="14" t="inlineStr">
+        <is>
+          <t>只</t>
+        </is>
+      </c>
+      <c r="I80" s="14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J80" s="14" t="inlineStr">
+        <is>
+          <t>“只是……罢了”表示事情不严重；“可是、还是”意思不对。</t>
+        </is>
+      </c>
+      <c r="K80" s="14" t="inlineStr">
+        <is>
+          <t>只是……罢了 means 'it's only…'; 可是 and 还是 do not fit.</t>
+        </is>
+      </c>
+      <c r="L80" s="14" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U07-3</t>
+        </is>
+      </c>
+      <c r="B81" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="C81" s="14" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="D81" s="14" t="inlineStr">
+        <is>
+          <t>你别担心，这不过是___罢了。</t>
+        </is>
+      </c>
+      <c r="E81" s="14" t="inlineStr">
+        <is>
+          <t>一次很重要的考试</t>
+        </is>
+      </c>
+      <c r="F81" s="14" t="inlineStr">
+        <is>
+          <t>一次小考试</t>
+        </is>
+      </c>
+      <c r="G81" s="14" t="inlineStr">
+        <is>
+          <t>最难的一次考试</t>
+        </is>
+      </c>
+      <c r="H81" s="14" t="inlineStr">
+        <is>
+          <t>决定一切的考试</t>
+        </is>
+      </c>
+      <c r="I81" s="14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J81" s="14" t="inlineStr">
+        <is>
+          <t>“不过……罢了”把事情说得很小、不严重，所以是“一次小考试”。</t>
+        </is>
+      </c>
+      <c r="K81" s="14" t="inlineStr">
+        <is>
+          <t>不过…罢了 plays something down, so "just a small quiz".</t>
+        </is>
+      </c>
+      <c r="L81" s="14" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U07-3</t>
+        </is>
+      </c>
+      <c r="B82" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="C82" s="14" t="inlineStr">
+        <is>
+          <t>找错</t>
+        </is>
+      </c>
+      <c r="D82" s="14" t="inlineStr">
+        <is>
+          <t>下面哪一句有错？</t>
+        </is>
+      </c>
+      <c r="E82" s="14" t="inlineStr">
+        <is>
+          <t>他只是不想去罢了，没有别的意思。</t>
+        </is>
+      </c>
+      <c r="F82" s="14" t="inlineStr">
+        <is>
+          <t>他只不过比我大两岁罢了。</t>
+        </is>
+      </c>
+      <c r="G82" s="14" t="inlineStr">
+        <is>
+          <t>这只不过是一场小雨罢了。</t>
+        </is>
+      </c>
+      <c r="H82" s="14" t="inlineStr">
+        <is>
+          <t>这件事很重要罢了，你一定要记住。</t>
+        </is>
+      </c>
+      <c r="I82" s="14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J82" s="14" t="inlineStr">
+        <is>
+          <t>“罢了”把事情说小，跟“很重要”矛盾，应去掉：这件事很重要，你一定要记住。</t>
+        </is>
+      </c>
+      <c r="K82" s="14" t="inlineStr">
+        <is>
+          <t>罢了 downplays and clashes with 很重要; drop it.</t>
+        </is>
+      </c>
+      <c r="L82" s="14" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U07-4</t>
+        </is>
+      </c>
+      <c r="B83" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="C83" s="14" t="inlineStr">
+        <is>
+          <t>辨析</t>
+        </is>
+      </c>
+      <c r="D83" s="14" t="inlineStr">
+        <is>
+          <t>他不但会说中文，___会说日语。</t>
+        </is>
+      </c>
+      <c r="E83" s="14" t="inlineStr">
+        <is>
+          <t>都</t>
+        </is>
+      </c>
+      <c r="F83" s="14" t="inlineStr">
+        <is>
+          <t>但是</t>
+        </is>
+      </c>
+      <c r="G83" s="14" t="inlineStr">
+        <is>
+          <t>还</t>
+        </is>
+      </c>
+      <c r="H83" s="14" t="inlineStr">
+        <is>
+          <t>就</t>
+        </is>
+      </c>
+      <c r="I83" s="14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J83" s="14" t="inlineStr">
+        <is>
+          <t>“不但”后面用“而且/还/也”表示更进一步；“但是”表示转折。</t>
+        </is>
+      </c>
+      <c r="K83" s="14" t="inlineStr">
+        <is>
+          <t>不但 is followed by 而且/还/也 to add more; 但是 marks a contrast.</t>
+        </is>
+      </c>
+      <c r="L83" s="14" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U07-4</t>
+        </is>
+      </c>
+      <c r="B84" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="C84" s="14" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="D84" s="14" t="inlineStr">
+        <is>
+          <t>这家饭馆不仅菜好吃，而且___。</t>
+        </is>
+      </c>
+      <c r="E84" s="14" t="inlineStr">
+        <is>
+          <t>价格也不贵</t>
+        </is>
+      </c>
+      <c r="F84" s="14" t="inlineStr">
+        <is>
+          <t>价格非常贵</t>
+        </is>
+      </c>
+      <c r="G84" s="14" t="inlineStr">
+        <is>
+          <t>服务很不好</t>
+        </is>
+      </c>
+      <c r="H84" s="14" t="inlineStr">
+        <is>
+          <t>环境很差</t>
+        </is>
+      </c>
+      <c r="I84" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J84" s="14" t="inlineStr">
+        <is>
+          <t>“不仅……而且……”前后意思要同一个方向，都是好的方面。</t>
+        </is>
+      </c>
+      <c r="K84" s="14" t="inlineStr">
+        <is>
+          <t>不仅……而且…… links points in the same direction, here both positive.</t>
+        </is>
+      </c>
+      <c r="L84" s="14" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U07-4</t>
+        </is>
+      </c>
+      <c r="B85" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="C85" s="14" t="inlineStr">
+        <is>
+          <t>找错</t>
+        </is>
+      </c>
+      <c r="D85" s="14" t="inlineStr">
+        <is>
+          <t>下面哪一句有错？</t>
+        </is>
+      </c>
+      <c r="E85" s="14" t="inlineStr">
+        <is>
+          <t>不仅我喜欢这本书，我的朋友也喜欢。</t>
+        </is>
+      </c>
+      <c r="F85" s="14" t="inlineStr">
+        <is>
+          <t>不但他会说中文，而且会说日语。</t>
+        </is>
+      </c>
+      <c r="G85" s="14" t="inlineStr">
+        <is>
+          <t>这家店的东西不但便宜，而且质量很好。</t>
+        </is>
+      </c>
+      <c r="H85" s="14" t="inlineStr">
+        <is>
+          <t>她不光会唱歌，还会跳舞。</t>
+        </is>
+      </c>
+      <c r="I85" s="14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J85" s="14" t="inlineStr">
+        <is>
+          <t>前后主语相同时，“不但”放在主语后面：他不但会说中文，而且会说日语。</t>
+        </is>
+      </c>
+      <c r="K85" s="14" t="inlineStr">
+        <is>
+          <t>With one subject, 不但 goes after it: 他不但会说中文……</t>
+        </is>
+      </c>
+      <c r="L85" s="14" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U08-1</t>
+        </is>
+      </c>
+      <c r="B86" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="C86" s="14" t="inlineStr">
+        <is>
+          <t>辨析</t>
+        </is>
+      </c>
+      <c r="D86" s="14" t="inlineStr">
+        <is>
+          <t>我们毕业以后就没联系了，___的事我就不知道了。</t>
+        </is>
+      </c>
+      <c r="E86" s="14" t="inlineStr">
+        <is>
+          <t>然后</t>
+        </is>
+      </c>
+      <c r="F86" s="14" t="inlineStr">
+        <is>
+          <t>再</t>
+        </is>
+      </c>
+      <c r="G86" s="14" t="inlineStr">
+        <is>
+          <t>后来</t>
+        </is>
+      </c>
+      <c r="H86" s="14" t="inlineStr">
+        <is>
+          <t>接着</t>
+        </is>
+      </c>
+      <c r="I86" s="14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J86" s="14" t="inlineStr">
+        <is>
+          <t>“后来”是时间名词，可以说“后来的事”；“然后、接着、再”只能连接动作，不能放在“的”前面。</t>
+        </is>
+      </c>
+      <c r="K86" s="14" t="inlineStr">
+        <is>
+          <t>后来 is a time noun, so 后来的事 works; 然后/接着/再 only link actions and can't take 的.</t>
+        </is>
+      </c>
+      <c r="L86" s="14" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U08-1</t>
+        </is>
+      </c>
+      <c r="B87" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="C87" s="14" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="D87" s="14" t="inlineStr">
+        <is>
+          <t>你先在这儿坐一会儿，然后___。</t>
+        </is>
+      </c>
+      <c r="E87" s="14" t="inlineStr">
+        <is>
+          <t>我们昨天去吃了饭</t>
+        </is>
+      </c>
+      <c r="F87" s="14" t="inlineStr">
+        <is>
+          <t>后来我们去吃饭了</t>
+        </is>
+      </c>
+      <c r="G87" s="14" t="inlineStr">
+        <is>
+          <t>我们再一起去吃饭</t>
+        </is>
+      </c>
+      <c r="H87" s="14" t="inlineStr">
+        <is>
+          <t>我们以前去吃过饭</t>
+        </is>
+      </c>
+      <c r="I87" s="14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J87" s="14" t="inlineStr">
+        <is>
+          <t>“然后”可以连接将来的两个动作，这里是安排，所以是“再一起去吃饭”；“后来”只说过去。</t>
+        </is>
+      </c>
+      <c r="K87" s="14" t="inlineStr">
+        <is>
+          <t>然后 can link two future actions; this is a plan, so "then we'll go eat together"; 后来 is only for the past.</t>
+        </is>
+      </c>
+      <c r="L87" s="14" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U08-1</t>
+        </is>
+      </c>
+      <c r="B88" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="C88" s="14" t="inlineStr">
+        <is>
+          <t>找错</t>
+        </is>
+      </c>
+      <c r="D88" s="14" t="inlineStr">
+        <is>
+          <t>下面哪一句有错？</t>
+        </is>
+      </c>
+      <c r="E88" s="14" t="inlineStr">
+        <is>
+          <t>你先洗手，后来再吃饭。</t>
+        </is>
+      </c>
+      <c r="F88" s="14" t="inlineStr">
+        <is>
+          <t>我们先去银行，然后去超市。</t>
+        </is>
+      </c>
+      <c r="G88" s="14" t="inlineStr">
+        <is>
+          <t>我以前不喜欢吃辣的，后来喜欢上了。</t>
+        </is>
+      </c>
+      <c r="H88" s="14" t="inlineStr">
+        <is>
+          <t>他去年去了上海，后来又去了广州。</t>
+        </is>
+      </c>
+      <c r="I88" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J88" s="14" t="inlineStr">
+        <is>
+          <t>“后来”只说过去，这里是将来的动作顺序，要用“然后”：你先洗手，然后再吃饭。</t>
+        </is>
+      </c>
+      <c r="K88" s="14" t="inlineStr">
+        <is>
+          <t>后来 is only for the past; a future sequence needs 然后.</t>
+        </is>
+      </c>
+      <c r="L88" s="14" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U08-2</t>
+        </is>
+      </c>
+      <c r="B89" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="C89" s="14" t="inlineStr">
+        <is>
+          <t>辨析</t>
+        </is>
+      </c>
+      <c r="D89" s="14" t="inlineStr">
+        <is>
+          <t>___明天下不下雨，我们都要出发。</t>
+        </is>
+      </c>
+      <c r="E89" s="14" t="inlineStr">
+        <is>
+          <t>即使</t>
+        </is>
+      </c>
+      <c r="F89" s="14" t="inlineStr">
+        <is>
+          <t>无论</t>
+        </is>
+      </c>
+      <c r="G89" s="14" t="inlineStr">
+        <is>
+          <t>因为</t>
+        </is>
+      </c>
+      <c r="H89" s="14" t="inlineStr">
+        <is>
+          <t>虽然</t>
+        </is>
+      </c>
+      <c r="I89" s="14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J89" s="14" t="inlineStr">
+        <is>
+          <t>“下不下雨”是正反问的形式，只能跟“无论/不管”配合，表示什么情况都一样。</t>
+        </is>
+      </c>
+      <c r="K89" s="14" t="inlineStr">
+        <is>
+          <t>An A-not-A phrase like 下不下雨 only works with 无论/不管 (whatever happens).</t>
+        </is>
+      </c>
+      <c r="L89" s="14" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U08-2</t>
+        </is>
+      </c>
+      <c r="B90" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="C90" s="14" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="D90" s="14" t="inlineStr">
+        <is>
+          <t>不管工作多忙，他___。</t>
+        </is>
+      </c>
+      <c r="E90" s="14" t="inlineStr">
+        <is>
+          <t>很少去跑步</t>
+        </is>
+      </c>
+      <c r="F90" s="14" t="inlineStr">
+        <is>
+          <t>每天都去跑步</t>
+        </is>
+      </c>
+      <c r="G90" s="14" t="inlineStr">
+        <is>
+          <t>每天去不去跑步</t>
+        </is>
+      </c>
+      <c r="H90" s="14" t="inlineStr">
+        <is>
+          <t>也许会去跑步</t>
+        </is>
+      </c>
+      <c r="I90" s="14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J90" s="14" t="inlineStr">
+        <is>
+          <t>“不管……”后面要用“都”说出不变的结果。</t>
+        </is>
+      </c>
+      <c r="K90" s="14" t="inlineStr">
+        <is>
+          <t>不管…… needs 都 with an unchanging result.</t>
+        </is>
+      </c>
+      <c r="L90" s="14" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U08-2</t>
+        </is>
+      </c>
+      <c r="B91" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="C91" s="14" t="inlineStr">
+        <is>
+          <t>找错</t>
+        </is>
+      </c>
+      <c r="D91" s="14" t="inlineStr">
+        <is>
+          <t>下面哪一句有错？</t>
+        </is>
+      </c>
+      <c r="E91" s="14" t="inlineStr">
+        <is>
+          <t>不管你去哪儿，我都跟着你。</t>
+        </is>
+      </c>
+      <c r="F91" s="14" t="inlineStr">
+        <is>
+          <t>不论天气怎么样，比赛都会进行。</t>
+        </is>
+      </c>
+      <c r="G91" s="14" t="inlineStr">
+        <is>
+          <t>无论天气很冷，他都去游泳。</t>
+        </is>
+      </c>
+      <c r="H91" s="14" t="inlineStr">
+        <is>
+          <t>无论谁问我，我都这么说。</t>
+        </is>
+      </c>
+      <c r="I91" s="14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J91" s="14" t="inlineStr">
+        <is>
+          <t>“无论”后面要用疑问词或正反形式，不能是确定的情况：无论天气多冷，他都去游泳。</t>
+        </is>
+      </c>
+      <c r="K91" s="14" t="inlineStr">
+        <is>
+          <t>无论 needs a question word or A-not-A, not a fixed fact: 无论天气多冷……</t>
+        </is>
+      </c>
+      <c r="L91" s="14" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U08-3</t>
+        </is>
+      </c>
+      <c r="B92" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="C92" s="14" t="inlineStr">
+        <is>
+          <t>辨析</t>
+        </is>
+      </c>
+      <c r="D92" s="14" t="inlineStr">
+        <is>
+          <t>我早就觉得他会迟到，他___迟到了。</t>
+        </is>
+      </c>
+      <c r="E92" s="14" t="inlineStr">
+        <is>
+          <t>竟然</t>
+        </is>
+      </c>
+      <c r="F92" s="14" t="inlineStr">
+        <is>
+          <t>果然</t>
+        </is>
+      </c>
+      <c r="G92" s="14" t="inlineStr">
+        <is>
+          <t>原来</t>
+        </is>
+      </c>
+      <c r="H92" s="14" t="inlineStr">
+        <is>
+          <t>居然</t>
+        </is>
+      </c>
+      <c r="I92" s="14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J92" s="14" t="inlineStr">
+        <is>
+          <t>事情跟预料的一样用“果然”；“竟然、居然”表示出乎意料。</t>
+        </is>
+      </c>
+      <c r="K92" s="14" t="inlineStr">
+        <is>
+          <t>果然 = as expected; 竟然/居然 mean unexpectedly.</t>
+        </is>
+      </c>
+      <c r="L92" s="14" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U08-3</t>
+        </is>
+      </c>
+      <c r="B93" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="C93" s="14" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="D93" s="14" t="inlineStr">
+        <is>
+          <t>我找了半天手机，原来___。</t>
+        </is>
+      </c>
+      <c r="E93" s="14" t="inlineStr">
+        <is>
+          <t>我一定能找到它</t>
+        </is>
+      </c>
+      <c r="F93" s="14" t="inlineStr">
+        <is>
+          <t>我明天再去找它</t>
+        </is>
+      </c>
+      <c r="G93" s="14" t="inlineStr">
+        <is>
+          <t>它就在我的包里</t>
+        </is>
+      </c>
+      <c r="H93" s="14" t="inlineStr">
+        <is>
+          <t>我得赶快去买新的</t>
+        </is>
+      </c>
+      <c r="I93" s="14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J93" s="14" t="inlineStr">
+        <is>
+          <t>“原来”表示发现了以前不知道的真实情况：手机原来就在包里。</t>
+        </is>
+      </c>
+      <c r="K93" s="14" t="inlineStr">
+        <is>
+          <t>原来 shows you have discovered the real situation: the phone was in my bag all along.</t>
+        </is>
+      </c>
+      <c r="L93" s="14" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U08-3</t>
+        </is>
+      </c>
+      <c r="B94" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="C94" s="14" t="inlineStr">
+        <is>
+          <t>找错</t>
+        </is>
+      </c>
+      <c r="D94" s="14" t="inlineStr">
+        <is>
+          <t>下面哪一句有错？</t>
+        </is>
+      </c>
+      <c r="E94" s="14" t="inlineStr">
+        <is>
+          <t>我以为他不会来，他果然来了。</t>
+        </is>
+      </c>
+      <c r="F94" s="14" t="inlineStr">
+        <is>
+          <t>他说今天会下雨，果然下雨了。</t>
+        </is>
+      </c>
+      <c r="G94" s="14" t="inlineStr">
+        <is>
+          <t>这么简单的题，他竟然做错了。</t>
+        </is>
+      </c>
+      <c r="H94" s="14" t="inlineStr">
+        <is>
+          <t>原来你们早就认识了！</t>
+        </is>
+      </c>
+      <c r="I94" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J94" s="14" t="inlineStr">
+        <is>
+          <t>跟原来想的相反，要用“竟然”：我以为他不会来，他竟然来了。</t>
+        </is>
+      </c>
+      <c r="K94" s="14" t="inlineStr">
+        <is>
+          <t>When it turns out opposite to what you thought, use 竟然: 我以为他不会来，他竟然来了。</t>
+        </is>
+      </c>
+      <c r="L94" s="14" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U08-4</t>
+        </is>
+      </c>
+      <c r="B95" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="C95" s="14" t="inlineStr">
+        <is>
+          <t>辨析</t>
+        </is>
+      </c>
+      <c r="D95" s="14" t="inlineStr">
+        <is>
+          <t>他的中文虽然不是最好的，但在我们班___不错的。</t>
+        </is>
+      </c>
+      <c r="E95" s="14" t="inlineStr">
+        <is>
+          <t>觉得</t>
+        </is>
+      </c>
+      <c r="F95" s="14" t="inlineStr">
+        <is>
+          <t>以为</t>
+        </is>
+      </c>
+      <c r="G95" s="14" t="inlineStr">
+        <is>
+          <t>算是</t>
+        </is>
+      </c>
+      <c r="H95" s="14" t="inlineStr">
+        <is>
+          <t>认为</t>
+        </is>
+      </c>
+      <c r="I95" s="14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J95" s="14" t="inlineStr">
+        <is>
+          <t>“算是”表示从某个角度评价；“认为、以为、觉得”前面要有人作主语。</t>
+        </is>
+      </c>
+      <c r="K95" s="14" t="inlineStr">
+        <is>
+          <t>算是 gives an evaluation; 认为/以为/觉得 need a person as subject.</t>
+        </is>
+      </c>
+      <c r="L95" s="14" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U08-4</t>
+        </is>
+      </c>
+      <c r="B96" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="C96" s="14" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="D96" s="14" t="inlineStr">
+        <is>
+          <t>来北京三年了，我也算是___了。</t>
+        </is>
+      </c>
+      <c r="E96" s="14" t="inlineStr">
+        <is>
+          <t>第一次来的人</t>
+        </is>
+      </c>
+      <c r="F96" s="14" t="inlineStr">
+        <is>
+          <t>半个北京人</t>
+        </is>
+      </c>
+      <c r="G96" s="14" t="inlineStr">
+        <is>
+          <t>北京的游客</t>
+        </is>
+      </c>
+      <c r="H96" s="14" t="inlineStr">
+        <is>
+          <t>刚来的外国人</t>
+        </is>
+      </c>
+      <c r="I96" s="14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J96" s="14" t="inlineStr">
+        <is>
+          <t>“算是”是对自己的评价，住了三年可以说是半个北京人。</t>
+        </is>
+      </c>
+      <c r="K96" s="14" t="inlineStr">
+        <is>
+          <t>算是 is a self-evaluation: after three years you count as half a Beijinger.</t>
+        </is>
+      </c>
+      <c r="L96" s="14" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U08-4</t>
+        </is>
+      </c>
+      <c r="B97" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="C97" s="14" t="inlineStr">
+        <is>
+          <t>找错</t>
+        </is>
+      </c>
+      <c r="D97" s="14" t="inlineStr">
+        <is>
+          <t>下面哪一句有错？</t>
+        </is>
+      </c>
+      <c r="E97" s="14" t="inlineStr">
+        <is>
+          <t>这个价格还算便宜。</t>
+        </is>
+      </c>
+      <c r="F97" s="14" t="inlineStr">
+        <is>
+          <t>我算是明天去上海。</t>
+        </is>
+      </c>
+      <c r="G97" s="14" t="inlineStr">
+        <is>
+          <t>他算是我最好的朋友。</t>
+        </is>
+      </c>
+      <c r="H97" s="14" t="inlineStr">
+        <is>
+          <t>今天的考试算比较简单。</t>
+        </is>
+      </c>
+      <c r="I97" s="14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J97" s="14" t="inlineStr">
+        <is>
+          <t>“算是”用来评价，不能说计划，应说：我打算明天去上海。</t>
+        </is>
+      </c>
+      <c r="K97" s="14" t="inlineStr">
+        <is>
+          <t>算是 evaluates; for a plan say 我打算明天去上海.</t>
+        </is>
+      </c>
+      <c r="L97" s="14" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U09-1</t>
+        </is>
+      </c>
+      <c r="B98" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="C98" s="14" t="inlineStr">
+        <is>
+          <t>辨析</t>
+        </is>
+      </c>
+      <c r="D98" s="14" t="inlineStr">
+        <is>
+          <t>这个菜___很好吃，我们点一个吧。</t>
+        </is>
+      </c>
+      <c r="E98" s="14" t="inlineStr">
+        <is>
+          <t>看下去</t>
+        </is>
+      </c>
+      <c r="F98" s="14" t="inlineStr">
+        <is>
+          <t>看起来</t>
+        </is>
+      </c>
+      <c r="G98" s="14" t="inlineStr">
+        <is>
+          <t>看见</t>
+        </is>
+      </c>
+      <c r="H98" s="14" t="inlineStr">
+        <is>
+          <t>看出来</t>
+        </is>
+      </c>
+      <c r="I98" s="14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J98" s="14" t="inlineStr">
+        <is>
+          <t>“看起来”表示从外表判断；“看出来”是看后发现、认出，“看见”只是看到。</t>
+        </is>
+      </c>
+      <c r="K98" s="14" t="inlineStr">
+        <is>
+          <t>看起来 means judging by appearance; 看出来 means to tell or recognize, and 看见 just means to see.</t>
+        </is>
+      </c>
+      <c r="L98" s="14" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U09-1</t>
+        </is>
+      </c>
+      <c r="B99" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="C99" s="14" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="D99" s="14" t="inlineStr">
+        <is>
+          <t>他看起来___，其实已经四十岁了。</t>
+        </is>
+      </c>
+      <c r="E99" s="14" t="inlineStr">
+        <is>
+          <t>有五十多岁</t>
+        </is>
+      </c>
+      <c r="F99" s="14" t="inlineStr">
+        <is>
+          <t>只有二十多岁</t>
+        </is>
+      </c>
+      <c r="G99" s="14" t="inlineStr">
+        <is>
+          <t>刚好四十岁</t>
+        </is>
+      </c>
+      <c r="H99" s="14" t="inlineStr">
+        <is>
+          <t>跟他的年龄差不多</t>
+        </is>
+      </c>
+      <c r="I99" s="14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J99" s="14" t="inlineStr">
+        <is>
+          <t>“看起来……其实……”表示外表跟真实情况相反，他看着比实际年轻。</t>
+        </is>
+      </c>
+      <c r="K99" s="14" t="inlineStr">
+        <is>
+          <t>看起来……其实…… contrasts looks with reality: he looks younger than he is.</t>
+        </is>
+      </c>
+      <c r="L99" s="14" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U09-1</t>
+        </is>
+      </c>
+      <c r="B100" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="C100" s="14" t="inlineStr">
+        <is>
+          <t>找错</t>
+        </is>
+      </c>
+      <c r="D100" s="14" t="inlineStr">
+        <is>
+          <t>下面哪一句有错？</t>
+        </is>
+      </c>
+      <c r="E100" s="14" t="inlineStr">
+        <is>
+          <t>我看起来这本书很有意思。</t>
+        </is>
+      </c>
+      <c r="F100" s="14" t="inlineStr">
+        <is>
+          <t>这件衣服看起来很贵。</t>
+        </is>
+      </c>
+      <c r="G100" s="14" t="inlineStr">
+        <is>
+          <t>你今天看起来很高兴。</t>
+        </is>
+      </c>
+      <c r="H100" s="14" t="inlineStr">
+        <is>
+          <t>天看起来要下雨了。</t>
+        </is>
+      </c>
+      <c r="I100" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J100" s="14" t="inlineStr">
+        <is>
+          <t>“看起来”的主语是被判断的事物，不是说话人：这本书看起来很有意思（或：我觉得……）。</t>
+        </is>
+      </c>
+      <c r="K100" s="14" t="inlineStr">
+        <is>
+          <t>The subject of 看起来 is the thing judged: 这本书看起来很有意思.</t>
+        </is>
+      </c>
+      <c r="L100" s="14" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U09-2</t>
+        </is>
+      </c>
+      <c r="B101" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="C101" s="14" t="inlineStr">
+        <is>
+          <t>辨析</t>
+        </is>
+      </c>
+      <c r="D101" s="14" t="inlineStr">
+        <is>
+          <t>路上堵车，我___没赶上飞机。</t>
+        </is>
+      </c>
+      <c r="E101" s="14" t="inlineStr">
+        <is>
+          <t>一下儿</t>
+        </is>
+      </c>
+      <c r="F101" s="14" t="inlineStr">
+        <is>
+          <t>差点儿</t>
+        </is>
+      </c>
+      <c r="G101" s="14" t="inlineStr">
+        <is>
+          <t>有点儿</t>
+        </is>
+      </c>
+      <c r="H101" s="14" t="inlineStr">
+        <is>
+          <t>一点儿</t>
+        </is>
+      </c>
+      <c r="I101" s="14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J101" s="14" t="inlineStr">
+        <is>
+          <t>“差点儿没赶上”表示几乎没赶上，最后赶上了；“有点儿、一点儿”没有这个意思。</t>
+        </is>
+      </c>
+      <c r="K101" s="14" t="inlineStr">
+        <is>
+          <t>差点儿没赶上 = almost missed (but made it); 有点儿 and 一点儿 cannot mean 'almost'.</t>
+        </is>
+      </c>
+      <c r="L101" s="14" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U09-2</t>
+        </is>
+      </c>
+      <c r="B102" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="C102" s="14" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="D102" s="14" t="inlineStr">
+        <is>
+          <t>今天早上我差点儿___，还好妈妈叫我了。</t>
+        </is>
+      </c>
+      <c r="E102" s="14" t="inlineStr">
+        <is>
+          <t>起晚了</t>
+        </is>
+      </c>
+      <c r="F102" s="14" t="inlineStr">
+        <is>
+          <t>准时起床</t>
+        </is>
+      </c>
+      <c r="G102" s="14" t="inlineStr">
+        <is>
+          <t>没睡好</t>
+        </is>
+      </c>
+      <c r="H102" s="14" t="inlineStr">
+        <is>
+          <t>起得很早</t>
+        </is>
+      </c>
+      <c r="I102" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J102" s="14" t="inlineStr">
+        <is>
+          <t>“差点儿”说几乎发生但没发生的事，妈妈叫了我，所以没有起晚。</t>
+        </is>
+      </c>
+      <c r="K102" s="14" t="inlineStr">
+        <is>
+          <t>差点儿 is for something that nearly happened; Mom woke me, so I didn't oversleep.</t>
+        </is>
+      </c>
+      <c r="L102" s="14" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U09-2</t>
+        </is>
+      </c>
+      <c r="B103" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="C103" s="14" t="inlineStr">
+        <is>
+          <t>找错</t>
+        </is>
+      </c>
+      <c r="D103" s="14" t="inlineStr">
+        <is>
+          <t>下面哪一句有错？</t>
+        </is>
+      </c>
+      <c r="E103" s="14" t="inlineStr">
+        <is>
+          <t>今天我差点儿迟到了，晚了十分钟。</t>
+        </is>
+      </c>
+      <c r="F103" s="14" t="inlineStr">
+        <is>
+          <t>他差点儿把手机丢了。</t>
+        </is>
+      </c>
+      <c r="G103" s="14" t="inlineStr">
+        <is>
+          <t>我们差点儿走错了路。</t>
+        </is>
+      </c>
+      <c r="H103" s="14" t="inlineStr">
+        <is>
+          <t>我们差点儿没赶上火车。</t>
+        </is>
+      </c>
+      <c r="I103" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J103" s="14" t="inlineStr">
+        <is>
+          <t>“差点儿迟到”是没迟到，后面却说晚了十分钟，矛盾，应说：今天我迟到了，晚了十分钟。</t>
+        </is>
+      </c>
+      <c r="K103" s="14" t="inlineStr">
+        <is>
+          <t>差点儿迟到 means not late, but 'ten minutes late' contradicts it; say 今天我迟到了.</t>
+        </is>
+      </c>
+      <c r="L103" s="14" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U09-3</t>
+        </is>
+      </c>
+      <c r="B104" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="C104" s="14" t="inlineStr">
+        <is>
+          <t>辨析</t>
+        </is>
+      </c>
+      <c r="D104" s="14" t="inlineStr">
+        <is>
+          <t>你看，这些花___漂亮啊！</t>
+        </is>
+      </c>
+      <c r="E104" s="14" t="inlineStr">
+        <is>
+          <t>太</t>
+        </is>
+      </c>
+      <c r="F104" s="14" t="inlineStr">
+        <is>
+          <t>怎么</t>
+        </is>
+      </c>
+      <c r="G104" s="14" t="inlineStr">
+        <is>
+          <t>多少</t>
+        </is>
+      </c>
+      <c r="H104" s="14" t="inlineStr">
+        <is>
+          <t>多</t>
+        </is>
+      </c>
+      <c r="I104" s="14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J104" s="14" t="inlineStr">
+        <is>
+          <t>感叹时用“多＋形容词＋啊”；“太”要跟“了”配合。</t>
+        </is>
+      </c>
+      <c r="K104" s="14" t="inlineStr">
+        <is>
+          <t>An exclamation uses 多 + adj + 啊; 太 needs 了.</t>
+        </is>
+      </c>
+      <c r="L104" s="14" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U09-3</t>
+        </is>
+      </c>
+      <c r="B105" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="C105" s="14" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="D105" s="14" t="inlineStr">
+        <is>
+          <t>要是能每天睡到十点，那该多___啊！</t>
+        </is>
+      </c>
+      <c r="E105" s="14" t="inlineStr">
+        <is>
+          <t>很好</t>
+        </is>
+      </c>
+      <c r="F105" s="14" t="inlineStr">
+        <is>
+          <t>好</t>
+        </is>
+      </c>
+      <c r="G105" s="14" t="inlineStr">
+        <is>
+          <t>好了</t>
+        </is>
+      </c>
+      <c r="H105" s="14" t="inlineStr">
+        <is>
+          <t>好的</t>
+        </is>
+      </c>
+      <c r="I105" s="14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J105" s="14" t="inlineStr">
+        <is>
+          <t>“多……啊”中间只放形容词，不加“了、很、的”。</t>
+        </is>
+      </c>
+      <c r="K105" s="14" t="inlineStr">
+        <is>
+          <t>多……啊 takes a bare adjective, without 了, 很 or 的.</t>
+        </is>
+      </c>
+      <c r="L105" s="14" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U09-3</t>
+        </is>
+      </c>
+      <c r="B106" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="C106" s="14" t="inlineStr">
+        <is>
+          <t>找错</t>
+        </is>
+      </c>
+      <c r="D106" s="14" t="inlineStr">
+        <is>
+          <t>下面哪一句有错？</t>
+        </is>
+      </c>
+      <c r="E106" s="14" t="inlineStr">
+        <is>
+          <t>这里的空气多新鲜啊！</t>
+        </is>
+      </c>
+      <c r="F106" s="14" t="inlineStr">
+        <is>
+          <t>今天多很热啊！</t>
+        </is>
+      </c>
+      <c r="G106" s="14" t="inlineStr">
+        <is>
+          <t>她的声音多好听啊！</t>
+        </is>
+      </c>
+      <c r="H106" s="14" t="inlineStr">
+        <is>
+          <t>你看，他跑得多快啊！</t>
+        </is>
+      </c>
+      <c r="I106" s="14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J106" s="14" t="inlineStr">
+        <is>
+          <t>“多”已经表示程度，不能再加“很”：今天多热啊！</t>
+        </is>
+      </c>
+      <c r="K106" s="14" t="inlineStr">
+        <is>
+          <t>多 already shows degree, so drop 很: 今天多热啊！</t>
+        </is>
+      </c>
+      <c r="L106" s="14" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U09-4</t>
+        </is>
+      </c>
+      <c r="B107" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="C107" s="14" t="inlineStr">
+        <is>
+          <t>辨析</t>
+        </is>
+      </c>
+      <c r="D107" s="14" t="inlineStr">
+        <is>
+          <t>请问您___是这所大学的学生？</t>
+        </is>
+      </c>
+      <c r="E107" s="14" t="inlineStr">
+        <is>
+          <t>是不是</t>
+        </is>
+      </c>
+      <c r="F107" s="14" t="inlineStr">
+        <is>
+          <t>有没有</t>
+        </is>
+      </c>
+      <c r="G107" s="14" t="inlineStr">
+        <is>
+          <t>是否</t>
+        </is>
+      </c>
+      <c r="H107" s="14" t="inlineStr">
+        <is>
+          <t>可不可以</t>
+        </is>
+      </c>
+      <c r="I107" s="14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J107" s="14" t="inlineStr">
+        <is>
+          <t>“是否”可以放在“是”前面，说“是否是”；“是不是是”重复了，“有没有、可不可以”不跟“是”搭配。</t>
+        </is>
+      </c>
+      <c r="K107" s="14" t="inlineStr">
+        <is>
+          <t>是否 can go before 是 (是否是…); 是不是是 repeats 是, and 有没有/可不可以 don't go with 是.</t>
+        </is>
+      </c>
+      <c r="L107" s="14" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U09-4</t>
+        </is>
+      </c>
+      <c r="B108" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="C108" s="14" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="D108" s="14" t="inlineStr">
+        <is>
+          <t>我们还不知道他是否___。</t>
+        </is>
+      </c>
+      <c r="E108" s="14" t="inlineStr">
+        <is>
+          <t>同意不同意这个计划</t>
+        </is>
+      </c>
+      <c r="F108" s="14" t="inlineStr">
+        <is>
+          <t>同意这个计划吗</t>
+        </is>
+      </c>
+      <c r="G108" s="14" t="inlineStr">
+        <is>
+          <t>同不同意这个计划</t>
+        </is>
+      </c>
+      <c r="H108" s="14" t="inlineStr">
+        <is>
+          <t>同意这个计划</t>
+        </is>
+      </c>
+      <c r="I108" s="14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J108" s="14" t="inlineStr">
+        <is>
+          <t>“是否”本身就有正反两面，后面不能再用正反问或“吗”。</t>
+        </is>
+      </c>
+      <c r="K108" s="14" t="inlineStr">
+        <is>
+          <t>是否 already means "whether or not", so it can't be followed by an A-not-A question or 吗.</t>
+        </is>
+      </c>
+      <c r="L108" s="14" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U09-4</t>
+        </is>
+      </c>
+      <c r="B109" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="C109" s="14" t="inlineStr">
+        <is>
+          <t>找错</t>
+        </is>
+      </c>
+      <c r="D109" s="14" t="inlineStr">
+        <is>
+          <t>下面哪一句有错？</t>
+        </is>
+      </c>
+      <c r="E109" s="14" t="inlineStr">
+        <is>
+          <t>我不知道这家店是否还开门。</t>
+        </is>
+      </c>
+      <c r="F109" s="14" t="inlineStr">
+        <is>
+          <t>请问您是否需要帮助？</t>
+        </is>
+      </c>
+      <c r="G109" s="14" t="inlineStr">
+        <is>
+          <t>我不知道他是否已经回国了。</t>
+        </is>
+      </c>
+      <c r="H109" s="14" t="inlineStr">
+        <is>
+          <t>你是否是中国人吗？</t>
+        </is>
+      </c>
+      <c r="I109" s="14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J109" s="14" t="inlineStr">
+        <is>
+          <t>“是否”已经表示疑问，不能再加“吗”：你是否是中国人？</t>
+        </is>
+      </c>
+      <c r="K109" s="14" t="inlineStr">
+        <is>
+          <t>是否 already asks the question, so drop 吗.</t>
+        </is>
+      </c>
+      <c r="L109" s="14" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U10-1</t>
+        </is>
+      </c>
+      <c r="B110" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="C110" s="14" t="inlineStr">
+        <is>
+          <t>辨析</t>
+        </is>
+      </c>
+      <c r="D110" s="14" t="inlineStr">
+        <is>
+          <t>他紧张得在房间里___，一刻也停不下来。</t>
+        </is>
+      </c>
+      <c r="E110" s="14" t="inlineStr">
+        <is>
+          <t>走一走</t>
+        </is>
+      </c>
+      <c r="F110" s="14" t="inlineStr">
+        <is>
+          <t>走过去</t>
+        </is>
+      </c>
+      <c r="G110" s="14" t="inlineStr">
+        <is>
+          <t>走来走去</t>
+        </is>
+      </c>
+      <c r="H110" s="14" t="inlineStr">
+        <is>
+          <t>走出来</t>
+        </is>
+      </c>
+      <c r="I110" s="14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J110" s="14" t="inlineStr">
+        <is>
+          <t>“动词＋来＋动词＋去”表示动作反复进行，正合“一刻也停不下来”；“走一走”是短时、轻松地走，“走过去”“走出来”只说一次移动的方向。</t>
+        </is>
+      </c>
+      <c r="K110" s="14" t="inlineStr">
+        <is>
+          <t>V来V去 means doing it back and forth over and over — matching 'couldn't stop for a moment'. 走一走 is a short, relaxed walk; 走过去 / 走出来 describe a single movement in one direction.</t>
+        </is>
+      </c>
+      <c r="L110" s="14" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U10-1</t>
+        </is>
+      </c>
+      <c r="B111" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="C111" s="14" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="D111" s="14" t="inlineStr">
+        <is>
+          <t>他找来找去，___。</t>
+        </is>
+      </c>
+      <c r="E111" s="14" t="inlineStr">
+        <is>
+          <t>很快就找着了</t>
+        </is>
+      </c>
+      <c r="F111" s="14" t="inlineStr">
+        <is>
+          <t>一下子就找到了</t>
+        </is>
+      </c>
+      <c r="G111" s="14" t="inlineStr">
+        <is>
+          <t>马上找到了钥匙</t>
+        </is>
+      </c>
+      <c r="H111" s="14" t="inlineStr">
+        <is>
+          <t>还是没找到钥匙</t>
+        </is>
+      </c>
+      <c r="I111" s="14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J111" s="14" t="inlineStr">
+        <is>
+          <t>“找来找去”表示找了很多次，跟“一下子、马上、很快”矛盾。</t>
+        </is>
+      </c>
+      <c r="K111" s="14" t="inlineStr">
+        <is>
+          <t>找来找去 means searching again and again, which clashes with 'at once' or 'quickly'.</t>
+        </is>
+      </c>
+      <c r="L111" s="14" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U10-1</t>
+        </is>
+      </c>
+      <c r="B112" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="C112" s="14" t="inlineStr">
+        <is>
+          <t>找错</t>
+        </is>
+      </c>
+      <c r="D112" s="14" t="inlineStr">
+        <is>
+          <t>下面哪一句有错？</t>
+        </is>
+      </c>
+      <c r="E112" s="14" t="inlineStr">
+        <is>
+          <t>我挑来挑去，最后买了一件红色的。</t>
+        </is>
+      </c>
+      <c r="F112" s="14" t="inlineStr">
+        <is>
+          <t>他们商量来商量去，还是决定坐火车去。</t>
+        </is>
+      </c>
+      <c r="G112" s="14" t="inlineStr">
+        <is>
+          <t>我看来看去了这本书。</t>
+        </is>
+      </c>
+      <c r="H112" s="14" t="inlineStr">
+        <is>
+          <t>孩子们在公园里跑来跑去。</t>
+        </is>
+      </c>
+      <c r="I112" s="14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J112" s="14" t="inlineStr">
+        <is>
+          <t>“看来看去”后面不能带宾语和“了”，应说：这本书我看来看去，……</t>
+        </is>
+      </c>
+      <c r="K112" s="14" t="inlineStr">
+        <is>
+          <t>看来看去 takes no object or 了 after it; say 这本书我看来看去……</t>
+        </is>
+      </c>
+      <c r="L112" s="14" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U10-2</t>
+        </is>
+      </c>
+      <c r="B113" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="C113" s="14" t="inlineStr">
+        <is>
+          <t>辨析</t>
+        </is>
+      </c>
+      <c r="D113" s="14" t="inlineStr">
+        <is>
+          <t>这个电影太没意思了，我实在看不___了。</t>
+        </is>
+      </c>
+      <c r="E113" s="14" t="inlineStr">
+        <is>
+          <t>下去</t>
+        </is>
+      </c>
+      <c r="F113" s="14" t="inlineStr">
+        <is>
+          <t>上去</t>
+        </is>
+      </c>
+      <c r="G113" s="14" t="inlineStr">
+        <is>
+          <t>起来</t>
+        </is>
+      </c>
+      <c r="H113" s="14" t="inlineStr">
+        <is>
+          <t>出来</t>
+        </is>
+      </c>
+      <c r="I113" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J113" s="14" t="inlineStr">
+        <is>
+          <t>“看不下去”表示没办法继续看了；“看不出来”是看不出、发现不了。</t>
+        </is>
+      </c>
+      <c r="K113" s="14" t="inlineStr">
+        <is>
+          <t>看不下去 means you can't go on watching; 看不出来 means you can't tell by looking.</t>
+        </is>
+      </c>
+      <c r="L113" s="14" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U10-2</t>
+        </is>
+      </c>
+      <c r="B114" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="C114" s="14" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="D114" s="14" t="inlineStr">
+        <is>
+          <t>你再这样___下去，身体会受不了的。</t>
+        </is>
+      </c>
+      <c r="E114" s="14" t="inlineStr">
+        <is>
+          <t>加过一次班</t>
+        </is>
+      </c>
+      <c r="F114" s="14" t="inlineStr">
+        <is>
+          <t>加了一天班</t>
+        </is>
+      </c>
+      <c r="G114" s="14" t="inlineStr">
+        <is>
+          <t>天天加班</t>
+        </is>
+      </c>
+      <c r="H114" s="14" t="inlineStr">
+        <is>
+          <t>昨天加班</t>
+        </is>
+      </c>
+      <c r="I114" s="14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J114" s="14" t="inlineStr">
+        <is>
+          <t>“下去”表示动作继续，前面要是能一直持续的事，比如“天天加班”；“加了一天班、昨天加班”已经结束了。</t>
+        </is>
+      </c>
+      <c r="K114" s="14" t="inlineStr">
+        <is>
+          <t>下去 means "keep on", so it needs an ongoing activity like working overtime every day, not a finished one-off.</t>
+        </is>
+      </c>
+      <c r="L114" s="14" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U10-2</t>
+        </is>
+      </c>
+      <c r="B115" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="C115" s="14" t="inlineStr">
+        <is>
+          <t>找错</t>
+        </is>
+      </c>
+      <c r="D115" s="14" t="inlineStr">
+        <is>
+          <t>下面哪一句有错？</t>
+        </is>
+      </c>
+      <c r="E115" s="14" t="inlineStr">
+        <is>
+          <t>你说得很好，请继续说下去。</t>
+        </is>
+      </c>
+      <c r="F115" s="14" t="inlineStr">
+        <is>
+          <t>他停下去，回头看了看我。</t>
+        </is>
+      </c>
+      <c r="G115" s="14" t="inlineStr">
+        <is>
+          <t>学中文很难，可是我会坚持下去。</t>
+        </is>
+      </c>
+      <c r="H115" s="14" t="inlineStr">
+        <is>
+          <t>这么热的天，我实在走不下去了。</t>
+        </is>
+      </c>
+      <c r="I115" s="14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J115" s="14" t="inlineStr">
+        <is>
+          <t>“停”要用“下来”：他停下来，回头看了看我。</t>
+        </is>
+      </c>
+      <c r="K115" s="14" t="inlineStr">
+        <is>
+          <t>停 takes 下来: 他停下来……</t>
+        </is>
+      </c>
+      <c r="L115" s="14" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U10-3</t>
+        </is>
+      </c>
+      <c r="B116" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="C116" s="14" t="inlineStr">
+        <is>
+          <t>辨析</t>
+        </is>
+      </c>
+      <c r="D116" s="14" t="inlineStr">
+        <is>
+          <t>他把所有的钱都___在买书上了。</t>
+        </is>
+      </c>
+      <c r="E116" s="14" t="inlineStr">
+        <is>
+          <t>给</t>
+        </is>
+      </c>
+      <c r="F116" s="14" t="inlineStr">
+        <is>
+          <t>花</t>
+        </is>
+      </c>
+      <c r="G116" s="14" t="inlineStr">
+        <is>
+          <t>买</t>
+        </is>
+      </c>
+      <c r="H116" s="14" t="inlineStr">
+        <is>
+          <t>付</t>
+        </is>
+      </c>
+      <c r="I116" s="14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J116" s="14" t="inlineStr">
+        <is>
+          <t>“把钱花在……上”是固定搭配，“买、给、付”不能这样用。</t>
+        </is>
+      </c>
+      <c r="K116" s="14" t="inlineStr">
+        <is>
+          <t>把钱花在……上 is the set pattern; 买, 给 and 付 do not fit it.</t>
+        </is>
+      </c>
+      <c r="L116" s="14" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U10-3</t>
+        </is>
+      </c>
+      <c r="B117" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="C117" s="14" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="D117" s="14" t="inlineStr">
+        <is>
+          <t>他把工资都浪费在___上了。</t>
+        </is>
+      </c>
+      <c r="E117" s="14" t="inlineStr">
+        <is>
+          <t>买没用的东西</t>
+        </is>
+      </c>
+      <c r="F117" s="14" t="inlineStr">
+        <is>
+          <t>给妈妈买礼物</t>
+        </is>
+      </c>
+      <c r="G117" s="14" t="inlineStr">
+        <is>
+          <t>交房租</t>
+        </is>
+      </c>
+      <c r="H117" s="14" t="inlineStr">
+        <is>
+          <t>孩子的学习</t>
+        </is>
+      </c>
+      <c r="I117" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J117" s="14" t="inlineStr">
+        <is>
+          <t>“浪费在……上”指把钱花在没用的事上；给妈妈买礼物、交房租、孩子的学习都是有用的。</t>
+        </is>
+      </c>
+      <c r="K117" s="14" t="inlineStr">
+        <is>
+          <t>浪费在…上 means spending on something useless; gifts for Mom, rent and a child's education are all useful.</t>
+        </is>
+      </c>
+      <c r="L117" s="14" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U10-3</t>
+        </is>
+      </c>
+      <c r="B118" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="C118" s="14" t="inlineStr">
+        <is>
+          <t>找错</t>
+        </is>
+      </c>
+      <c r="D118" s="14" t="inlineStr">
+        <is>
+          <t>下面哪一句有错？</t>
+        </is>
+      </c>
+      <c r="E118" s="14" t="inlineStr">
+        <is>
+          <t>我把周末都花在了学中文上。</t>
+        </is>
+      </c>
+      <c r="F118" s="14" t="inlineStr">
+        <is>
+          <t>他把一个月的工资都花在了衣服上。</t>
+        </is>
+      </c>
+      <c r="G118" s="14" t="inlineStr">
+        <is>
+          <t>不要把时间浪费在不重要的事情上。</t>
+        </is>
+      </c>
+      <c r="H118" s="14" t="inlineStr">
+        <is>
+          <t>他把很多钱花在买游戏。</t>
+        </is>
+      </c>
+      <c r="I118" s="14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J118" s="14" t="inlineStr">
+        <is>
+          <t>“花在……上”不能少“上”：他把很多钱花在买游戏上。</t>
+        </is>
+      </c>
+      <c r="K118" s="14" t="inlineStr">
+        <is>
+          <t>花在…上 needs 上: 他把很多钱花在买游戏上.</t>
+        </is>
+      </c>
+      <c r="L118" s="14" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U10-4</t>
+        </is>
+      </c>
+      <c r="B119" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="C119" s="14" t="inlineStr">
+        <is>
+          <t>辨析</t>
+        </is>
+      </c>
+      <c r="D119" s="14" t="inlineStr">
+        <is>
+          <t>___明天下大雨，我也要去爬山。</t>
+        </is>
+      </c>
+      <c r="E119" s="14" t="inlineStr">
+        <is>
+          <t>既然</t>
+        </is>
+      </c>
+      <c r="F119" s="14" t="inlineStr">
+        <is>
+          <t>只要</t>
+        </is>
+      </c>
+      <c r="G119" s="14" t="inlineStr">
+        <is>
+          <t>因为</t>
+        </is>
+      </c>
+      <c r="H119" s="14" t="inlineStr">
+        <is>
+          <t>即使</t>
+        </is>
+      </c>
+      <c r="I119" s="14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J119" s="14" t="inlineStr">
+        <is>
+          <t>“即使……也……”表示假设，就算下大雨也不改变；“只要”后面用“就”，“既然”说已知事实。</t>
+        </is>
+      </c>
+      <c r="K119" s="14" t="inlineStr">
+        <is>
+          <t>即使…也… means "even if"; 只要 pairs with 就, and 既然 states a known fact.</t>
+        </is>
+      </c>
+      <c r="L119" s="14" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U10-4</t>
+        </is>
+      </c>
+      <c r="B120" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="C120" s="14" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="D120" s="14" t="inlineStr">
+        <is>
+          <t>即使你不喜欢这个工作，___。</t>
+        </is>
+      </c>
+      <c r="E120" s="14" t="inlineStr">
+        <is>
+          <t>但是不用做</t>
+        </is>
+      </c>
+      <c r="F120" s="14" t="inlineStr">
+        <is>
+          <t>就换一个吧</t>
+        </is>
+      </c>
+      <c r="G120" s="14" t="inlineStr">
+        <is>
+          <t>也要认真做完</t>
+        </is>
+      </c>
+      <c r="H120" s="14" t="inlineStr">
+        <is>
+          <t>所以别做了</t>
+        </is>
+      </c>
+      <c r="I120" s="14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J120" s="14" t="inlineStr">
+        <is>
+          <t>“即使”后面要用“也”说不变的结果。</t>
+        </is>
+      </c>
+      <c r="K120" s="14" t="inlineStr">
+        <is>
+          <t>即使 needs 也 with an unchanged result.</t>
+        </is>
+      </c>
+      <c r="L120" s="14" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U10-4</t>
+        </is>
+      </c>
+      <c r="B121" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="C121" s="14" t="inlineStr">
+        <is>
+          <t>找错</t>
+        </is>
+      </c>
+      <c r="D121" s="14" t="inlineStr">
+        <is>
+          <t>下面哪一句有错？</t>
+        </is>
+      </c>
+      <c r="E121" s="14" t="inlineStr">
+        <is>
+          <t>即使失败了，也没关系。</t>
+        </is>
+      </c>
+      <c r="F121" s="14" t="inlineStr">
+        <is>
+          <t>即使很累，他也坚持跑步。</t>
+        </is>
+      </c>
+      <c r="G121" s="14" t="inlineStr">
+        <is>
+          <t>即使你不说，我也知道。</t>
+        </is>
+      </c>
+      <c r="H121" s="14" t="inlineStr">
+        <is>
+          <t>即使他已经来了，就让他进来吧。</t>
+        </is>
+      </c>
+      <c r="I121" s="14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J121" s="14" t="inlineStr">
+        <is>
+          <t>已经是事实，后面又用“就”，应该用“既然”：既然他已经来了，就让他进来吧。</t>
+        </is>
+      </c>
+      <c r="K121" s="14" t="inlineStr">
+        <is>
+          <t>It is already a fact and is followed by 就, so use 既然.</t>
+        </is>
+      </c>
+      <c r="L121" s="14" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U11-1</t>
+        </is>
+      </c>
+      <c r="B122" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="C122" s="14" t="inlineStr">
+        <is>
+          <t>辨析</t>
+        </is>
+      </c>
+      <c r="D122" s="14" t="inlineStr">
+        <is>
+          <t>周末你想几点起床___几点起床。</t>
+        </is>
+      </c>
+      <c r="E122" s="14" t="inlineStr">
+        <is>
+          <t>再</t>
+        </is>
+      </c>
+      <c r="F122" s="14" t="inlineStr">
+        <is>
+          <t>都</t>
+        </is>
+      </c>
+      <c r="G122" s="14" t="inlineStr">
+        <is>
+          <t>才</t>
+        </is>
+      </c>
+      <c r="H122" s="14" t="inlineStr">
+        <is>
+          <t>就</t>
+        </is>
+      </c>
+      <c r="I122" s="14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J122" s="14" t="inlineStr">
+        <is>
+          <t>“想……就……”表示随意，前后用同一个疑问词。</t>
+        </is>
+      </c>
+      <c r="K122" s="14" t="inlineStr">
+        <is>
+          <t>想……就…… means 'whatever you like', with the same question word twice.</t>
+        </is>
+      </c>
+      <c r="L122" s="14" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U11-1</t>
+        </is>
+      </c>
+      <c r="B123" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="C123" s="14" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="D123" s="14" t="inlineStr">
+        <is>
+          <t>这儿的衣服你想买哪件就___。</t>
+        </is>
+      </c>
+      <c r="E123" s="14" t="inlineStr">
+        <is>
+          <t>买一件</t>
+        </is>
+      </c>
+      <c r="F123" s="14" t="inlineStr">
+        <is>
+          <t>买这件</t>
+        </is>
+      </c>
+      <c r="G123" s="14" t="inlineStr">
+        <is>
+          <t>买什么</t>
+        </is>
+      </c>
+      <c r="H123" s="14" t="inlineStr">
+        <is>
+          <t>买哪件</t>
+        </is>
+      </c>
+      <c r="I123" s="14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J123" s="14" t="inlineStr">
+        <is>
+          <t>“想……就……”前后要用同一个疑问词，前面是“哪件”，后面也是“哪件”。</t>
+        </is>
+      </c>
+      <c r="K123" s="14" t="inlineStr">
+        <is>
+          <t>The same question word must repeat: 哪件……哪件.</t>
+        </is>
+      </c>
+      <c r="L123" s="14" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U11-1</t>
+        </is>
+      </c>
+      <c r="B124" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="C124" s="14" t="inlineStr">
+        <is>
+          <t>找错</t>
+        </is>
+      </c>
+      <c r="D124" s="14" t="inlineStr">
+        <is>
+          <t>下面哪一句有错？</t>
+        </is>
+      </c>
+      <c r="E124" s="14" t="inlineStr">
+        <is>
+          <t>他想什么时候来就什么时候来。</t>
+        </is>
+      </c>
+      <c r="F124" s="14" t="inlineStr">
+        <is>
+          <t>你想看什么就看哪个。</t>
+        </is>
+      </c>
+      <c r="G124" s="14" t="inlineStr">
+        <is>
+          <t>你想坐哪儿就坐哪儿。</t>
+        </is>
+      </c>
+      <c r="H124" s="14" t="inlineStr">
+        <is>
+          <t>想吃什么就点什么吧。</t>
+        </is>
+      </c>
+      <c r="I124" s="14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J124" s="14" t="inlineStr">
+        <is>
+          <t>前后疑问词要一样：你想看什么就看什么。</t>
+        </is>
+      </c>
+      <c r="K124" s="14" t="inlineStr">
+        <is>
+          <t>The question words must match: 想看什么就看什么.</t>
+        </is>
+      </c>
+      <c r="L124" s="14" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U11-2</t>
+        </is>
+      </c>
+      <c r="B125" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="C125" s="14" t="inlineStr">
+        <is>
+          <t>辨析</t>
+        </is>
+      </c>
+      <c r="D125" s="14" t="inlineStr">
+        <is>
+          <t>别___看书，对眼睛不好。</t>
+        </is>
+      </c>
+      <c r="E125" s="14" t="inlineStr">
+        <is>
+          <t>躺过</t>
+        </is>
+      </c>
+      <c r="F125" s="14" t="inlineStr">
+        <is>
+          <t>躺着</t>
+        </is>
+      </c>
+      <c r="G125" s="14" t="inlineStr">
+        <is>
+          <t>躺了</t>
+        </is>
+      </c>
+      <c r="H125" s="14" t="inlineStr">
+        <is>
+          <t>在躺</t>
+        </is>
+      </c>
+      <c r="I125" s="14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J125" s="14" t="inlineStr">
+        <is>
+          <t>“动词1＋着＋动词2”表示用什么方式做，所以是“躺着看书”。</t>
+        </is>
+      </c>
+      <c r="K125" s="14" t="inlineStr">
+        <is>
+          <t>Verb1 + 着 + verb2 shows the manner, so 躺着看书.</t>
+        </is>
+      </c>
+      <c r="L125" s="14" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U11-2</t>
+        </is>
+      </c>
+      <c r="B126" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="C126" s="14" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="D126" s="14" t="inlineStr">
+        <is>
+          <t>他笑着___。</t>
+        </is>
+      </c>
+      <c r="E126" s="14" t="inlineStr">
+        <is>
+          <t>一直很高兴</t>
+        </is>
+      </c>
+      <c r="F126" s="14" t="inlineStr">
+        <is>
+          <t>跟我说再见</t>
+        </is>
+      </c>
+      <c r="G126" s="14" t="inlineStr">
+        <is>
+          <t>笑得很开心</t>
+        </is>
+      </c>
+      <c r="H126" s="14" t="inlineStr">
+        <is>
+          <t>是好朋友</t>
+        </is>
+      </c>
+      <c r="I126" s="14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J126" s="14" t="inlineStr">
+        <is>
+          <t>“V1着”后面要接另一个具体动作，表示用这种方式做这件事。</t>
+        </is>
+      </c>
+      <c r="K126" s="14" t="inlineStr">
+        <is>
+          <t>V1着 must be followed by another concrete action done in that manner.</t>
+        </is>
+      </c>
+      <c r="L126" s="14" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U11-2</t>
+        </is>
+      </c>
+      <c r="B127" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="C127" s="14" t="inlineStr">
+        <is>
+          <t>找错</t>
+        </is>
+      </c>
+      <c r="D127" s="14" t="inlineStr">
+        <is>
+          <t>下面哪一句有错？</t>
+        </is>
+      </c>
+      <c r="E127" s="14" t="inlineStr">
+        <is>
+          <t>她听着音乐做作业。</t>
+        </is>
+      </c>
+      <c r="F127" s="14" t="inlineStr">
+        <is>
+          <t>我们走着去学校吧。</t>
+        </is>
+      </c>
+      <c r="G127" s="14" t="inlineStr">
+        <is>
+          <t>孩子们唱着歌走进了教室。</t>
+        </is>
+      </c>
+      <c r="H127" s="14" t="inlineStr">
+        <is>
+          <t>他站着了跟我说话。</t>
+        </is>
+      </c>
+      <c r="I127" s="14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J127" s="14" t="inlineStr">
+        <is>
+          <t>“着”后面不能再加“了”：他站着跟我说话。</t>
+        </is>
+      </c>
+      <c r="K127" s="14" t="inlineStr">
+        <is>
+          <t>No 了 after 着: 他站着跟我说话.</t>
+        </is>
+      </c>
+      <c r="L127" s="14" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U11-3</t>
+        </is>
+      </c>
+      <c r="B128" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="C128" s="14" t="inlineStr">
+        <is>
+          <t>辨析</t>
+        </is>
+      </c>
+      <c r="D128" s="14" t="inlineStr">
+        <is>
+          <t>我___选择这家公司，是因为这里的人很好。</t>
+        </is>
+      </c>
+      <c r="E128" s="14" t="inlineStr">
+        <is>
+          <t>因为</t>
+        </is>
+      </c>
+      <c r="F128" s="14" t="inlineStr">
+        <is>
+          <t>因此</t>
+        </is>
+      </c>
+      <c r="G128" s="14" t="inlineStr">
+        <is>
+          <t>由于</t>
+        </is>
+      </c>
+      <c r="H128" s="14" t="inlineStr">
+        <is>
+          <t>之所以</t>
+        </is>
+      </c>
+      <c r="I128" s="14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J128" s="14" t="inlineStr">
+        <is>
+          <t>前面是结果、后面“是因为”说原因，前面要用“之所以”；“因此”表示结果，不能跟“是因为”配合。</t>
+        </is>
+      </c>
+      <c r="K128" s="14" t="inlineStr">
+        <is>
+          <t>When the second clause gives the reason with 是因为, the first needs 之所以; 因此 marks a result and can't pair with 是因为.</t>
+        </is>
+      </c>
+      <c r="L128" s="14" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U11-3</t>
+        </is>
+      </c>
+      <c r="B129" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="C129" s="14" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="D129" s="14" t="inlineStr">
+        <is>
+          <t>他之所以学习这么努力，___。</t>
+        </is>
+      </c>
+      <c r="E129" s="14" t="inlineStr">
+        <is>
+          <t>所以他的成绩很好</t>
+        </is>
+      </c>
+      <c r="F129" s="14" t="inlineStr">
+        <is>
+          <t>是因为他想去留学</t>
+        </is>
+      </c>
+      <c r="G129" s="14" t="inlineStr">
+        <is>
+          <t>因此他每天都很累</t>
+        </is>
+      </c>
+      <c r="H129" s="14" t="inlineStr">
+        <is>
+          <t>但是他的成绩不好</t>
+        </is>
+      </c>
+      <c r="I129" s="14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J129" s="14" t="inlineStr">
+        <is>
+          <t>“之所以”后面必须用“是因为”说出原因。</t>
+        </is>
+      </c>
+      <c r="K129" s="14" t="inlineStr">
+        <is>
+          <t>之所以 must be followed by 是因为 giving the reason.</t>
+        </is>
+      </c>
+      <c r="L129" s="14" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U11-3</t>
+        </is>
+      </c>
+      <c r="B130" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="C130" s="14" t="inlineStr">
+        <is>
+          <t>找错</t>
+        </is>
+      </c>
+      <c r="D130" s="14" t="inlineStr">
+        <is>
+          <t>下面哪一句有错？</t>
+        </is>
+      </c>
+      <c r="E130" s="14" t="inlineStr">
+        <is>
+          <t>这个地方之所以有名，是因为这里的风景很美。</t>
+        </is>
+      </c>
+      <c r="F130" s="14" t="inlineStr">
+        <is>
+          <t>他之所以没来，是因为生病了。</t>
+        </is>
+      </c>
+      <c r="G130" s="14" t="inlineStr">
+        <is>
+          <t>之所以下雨，所以比赛取消了。</t>
+        </is>
+      </c>
+      <c r="H130" s="14" t="inlineStr">
+        <is>
+          <t>我之所以喜欢这座城市，是因为这里很安静。</t>
+        </is>
+      </c>
+      <c r="I130" s="14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J130" s="14" t="inlineStr">
+        <is>
+          <t>“之所以”后面是结果，不是原因，应说：因为下雨，所以比赛取消了。</t>
+        </is>
+      </c>
+      <c r="K130" s="14" t="inlineStr">
+        <is>
+          <t>之所以 introduces a result, not a cause; say 因为下雨，所以比赛取消了.</t>
+        </is>
+      </c>
+      <c r="L130" s="14" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U11-4</t>
+        </is>
+      </c>
+      <c r="B131" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="C131" s="14" t="inlineStr">
+        <is>
+          <t>辨析</t>
+        </is>
+      </c>
+      <c r="D131" s="14" t="inlineStr">
+        <is>
+          <t>这次旅行我们___上海为第一站。</t>
+        </is>
+      </c>
+      <c r="E131" s="14" t="inlineStr">
+        <is>
+          <t>把</t>
+        </is>
+      </c>
+      <c r="F131" s="14" t="inlineStr">
+        <is>
+          <t>以</t>
+        </is>
+      </c>
+      <c r="G131" s="14" t="inlineStr">
+        <is>
+          <t>对</t>
+        </is>
+      </c>
+      <c r="H131" s="14" t="inlineStr">
+        <is>
+          <t>用</t>
+        </is>
+      </c>
+      <c r="I131" s="14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J131" s="14" t="inlineStr">
+        <is>
+          <t>固定格式是“以A为B”，把A当作B；“把”要说“把……作为”。</t>
+        </is>
+      </c>
+      <c r="K131" s="14" t="inlineStr">
+        <is>
+          <t>The set pattern is 以A为B; 把 would need 把……作为.</t>
+        </is>
+      </c>
+      <c r="L131" s="14" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U11-4</t>
+        </is>
+      </c>
+      <c r="B132" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="C132" s="14" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="D132" s="14" t="inlineStr">
+        <is>
+          <t>这家饭馆的菜以___为主。</t>
+        </is>
+      </c>
+      <c r="E132" s="14" t="inlineStr">
+        <is>
+          <t>很好吃</t>
+        </is>
+      </c>
+      <c r="F132" s="14" t="inlineStr">
+        <is>
+          <t>非常便宜</t>
+        </is>
+      </c>
+      <c r="G132" s="14" t="inlineStr">
+        <is>
+          <t>环境好</t>
+        </is>
+      </c>
+      <c r="H132" s="14" t="inlineStr">
+        <is>
+          <t>四川菜</t>
+        </is>
+      </c>
+      <c r="I132" s="14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J132" s="14" t="inlineStr">
+        <is>
+          <t>“以……为主”中间要放名词，说明主要是什么。</t>
+        </is>
+      </c>
+      <c r="K132" s="14" t="inlineStr">
+        <is>
+          <t>以……为主 takes a noun saying what is the main part.</t>
+        </is>
+      </c>
+      <c r="L132" s="14" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U11-4</t>
+        </is>
+      </c>
+      <c r="B133" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="C133" s="14" t="inlineStr">
+        <is>
+          <t>找错</t>
+        </is>
+      </c>
+      <c r="D133" s="14" t="inlineStr">
+        <is>
+          <t>下面哪一句有错？</t>
+        </is>
+      </c>
+      <c r="E133" s="14" t="inlineStr">
+        <is>
+          <t>我们以这家饭馆为见面地点。</t>
+        </is>
+      </c>
+      <c r="F133" s="14" t="inlineStr">
+        <is>
+          <t>我们以这座山为目标，今天一定要爬上去。</t>
+        </is>
+      </c>
+      <c r="G133" s="14" t="inlineStr">
+        <is>
+          <t>这次比赛以友谊为主。</t>
+        </is>
+      </c>
+      <c r="H133" s="14" t="inlineStr">
+        <is>
+          <t>我们以为北京第一站。</t>
+        </is>
+      </c>
+      <c r="I133" s="14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J133" s="14" t="inlineStr">
+        <is>
+          <t>“以”和“为”要分开，中间放A：我们以北京为第一站。</t>
+        </is>
+      </c>
+      <c r="K133" s="14" t="inlineStr">
+        <is>
+          <t>以 and 为 must be split with A in between: 以北京为第一站.</t>
+        </is>
+      </c>
+      <c r="L133" s="14" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U12-1</t>
+        </is>
+      </c>
+      <c r="B134" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="C134" s="14" t="inlineStr">
+        <is>
+          <t>辨析</t>
+        </is>
+      </c>
+      <c r="D134" s="14" t="inlineStr">
+        <is>
+          <t>A：你怕不怕狗？B：我___不怕呢！</t>
+        </is>
+      </c>
+      <c r="E134" s="14" t="inlineStr">
+        <is>
+          <t>都</t>
+        </is>
+      </c>
+      <c r="F134" s="14" t="inlineStr">
+        <is>
+          <t>就</t>
+        </is>
+      </c>
+      <c r="G134" s="14" t="inlineStr">
+        <is>
+          <t>再</t>
+        </is>
+      </c>
+      <c r="H134" s="14" t="inlineStr">
+        <is>
+          <t>才</t>
+        </is>
+      </c>
+      <c r="I134" s="14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J134" s="14" t="inlineStr">
+        <is>
+          <t>“才……呢”加强语气，表示坚决否定对方的想法。</t>
+        </is>
+      </c>
+      <c r="K134" s="14" t="inlineStr">
+        <is>
+          <t>才……呢 adds emphasis, firmly rejecting the other person's idea.</t>
+        </is>
+      </c>
+      <c r="L134" s="14" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U12-1</t>
+        </is>
+      </c>
+      <c r="B135" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="C135" s="14" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="D135" s="14" t="inlineStr">
+        <is>
+          <t>A：这件衣服太贵了吧？B：一百块钱才___呢！</t>
+        </is>
+      </c>
+      <c r="E135" s="14" t="inlineStr">
+        <is>
+          <t>太贵了</t>
+        </is>
+      </c>
+      <c r="F135" s="14" t="inlineStr">
+        <is>
+          <t>很贵</t>
+        </is>
+      </c>
+      <c r="G135" s="14" t="inlineStr">
+        <is>
+          <t>贵</t>
+        </is>
+      </c>
+      <c r="H135" s="14" t="inlineStr">
+        <is>
+          <t>不贵</t>
+        </is>
+      </c>
+      <c r="I135" s="14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J135" s="14" t="inlineStr">
+        <is>
+          <t>B在反驳A，“才……呢”强调相反的看法，所以是“才不贵呢”。</t>
+        </is>
+      </c>
+      <c r="K135" s="14" t="inlineStr">
+        <is>
+          <t>B is contradicting A, so 才……呢 stresses the opposite: 才不贵呢.</t>
+        </is>
+      </c>
+      <c r="L135" s="14" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U12-1</t>
+        </is>
+      </c>
+      <c r="B136" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="C136" s="14" t="inlineStr">
+        <is>
+          <t>找错</t>
+        </is>
+      </c>
+      <c r="D136" s="14" t="inlineStr">
+        <is>
+          <t>下面哪一句有错？</t>
+        </is>
+      </c>
+      <c r="E136" s="14" t="inlineStr">
+        <is>
+          <t>我才不喜欢吃苹果吗？</t>
+        </is>
+      </c>
+      <c r="F136" s="14" t="inlineStr">
+        <is>
+          <t>他说的才对呢。</t>
+        </is>
+      </c>
+      <c r="G136" s="14" t="inlineStr">
+        <is>
+          <t>我才不相信他的话呢！</t>
+        </is>
+      </c>
+      <c r="H136" s="14" t="inlineStr">
+        <is>
+          <t>这才是好办法呢！</t>
+        </is>
+      </c>
+      <c r="I136" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J136" s="14" t="inlineStr">
+        <is>
+          <t>“才……”的强调句句末用“呢”，不用“吗”：我才不喜欢吃苹果呢！</t>
+        </is>
+      </c>
+      <c r="K136" s="14" t="inlineStr">
+        <is>
+          <t>Emphatic 才 ends with 呢, not 吗.</t>
+        </is>
+      </c>
+      <c r="L136" s="14" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U12-2</t>
+        </is>
+      </c>
+      <c r="B137" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="C137" s="14" t="inlineStr">
+        <is>
+          <t>辨析</t>
+        </is>
+      </c>
+      <c r="D137" s="14" t="inlineStr">
+        <is>
+          <t>只是一点儿小事，你___这么生气呢？</t>
+        </is>
+      </c>
+      <c r="E137" s="14" t="inlineStr">
+        <is>
+          <t>何必</t>
+        </is>
+      </c>
+      <c r="F137" s="14" t="inlineStr">
+        <is>
+          <t>不用</t>
+        </is>
+      </c>
+      <c r="G137" s="14" t="inlineStr">
+        <is>
+          <t>不必</t>
+        </is>
+      </c>
+      <c r="H137" s="14" t="inlineStr">
+        <is>
+          <t>必须</t>
+        </is>
+      </c>
+      <c r="I137" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J137" s="14" t="inlineStr">
+        <is>
+          <t>“何必……呢”是反问，表示没必要；“不必、不用”不用在反问句里。</t>
+        </is>
+      </c>
+      <c r="K137" s="14" t="inlineStr">
+        <is>
+          <t>何必……呢 is rhetorical ('why bother'); 不必 and 不用 are not used in rhetorical questions.</t>
+        </is>
+      </c>
+      <c r="L137" s="14" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U12-2</t>
+        </is>
+      </c>
+      <c r="B138" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="C138" s="14" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="D138" s="14" t="inlineStr">
+        <is>
+          <t>___，何必再买一个新的呢？</t>
+        </is>
+      </c>
+      <c r="E138" s="14" t="inlineStr">
+        <is>
+          <t>新手机现在正打折</t>
+        </is>
+      </c>
+      <c r="F138" s="14" t="inlineStr">
+        <is>
+          <t>你的手机已经坏了</t>
+        </is>
+      </c>
+      <c r="G138" s="14" t="inlineStr">
+        <is>
+          <t>你一直想要新手机</t>
+        </is>
+      </c>
+      <c r="H138" s="14" t="inlineStr">
+        <is>
+          <t>你的手机还能用</t>
+        </is>
+      </c>
+      <c r="I138" s="14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J138" s="14" t="inlineStr">
+        <is>
+          <t>“何必……呢”表示没有必要，前面要给出不必做的理由：手机还能用。</t>
+        </is>
+      </c>
+      <c r="K138" s="14" t="inlineStr">
+        <is>
+          <t>何必…呢 means "there's no need", so the first part gives a reason not to: the phone still works.</t>
+        </is>
+      </c>
+      <c r="L138" s="14" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U12-2</t>
+        </is>
+      </c>
+      <c r="B139" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="C139" s="14" t="inlineStr">
+        <is>
+          <t>找错</t>
+        </is>
+      </c>
+      <c r="D139" s="14" t="inlineStr">
+        <is>
+          <t>下面哪一句有错？</t>
+        </is>
+      </c>
+      <c r="E139" s="14" t="inlineStr">
+        <is>
+          <t>你何必为这点儿小事难过呢？</t>
+        </is>
+      </c>
+      <c r="F139" s="14" t="inlineStr">
+        <is>
+          <t>我们走着去就行，何必坐出租车呢？</t>
+        </is>
+      </c>
+      <c r="G139" s="14" t="inlineStr">
+        <is>
+          <t>你何必这么着急吗？</t>
+        </is>
+      </c>
+      <c r="H139" s="14" t="inlineStr">
+        <is>
+          <t>他已经知道错了，何必再说他呢？</t>
+        </is>
+      </c>
+      <c r="I139" s="14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J139" s="14" t="inlineStr">
+        <is>
+          <t>“何必”句末用“呢”，不用“吗”：你何必这么着急呢？</t>
+        </is>
+      </c>
+      <c r="K139" s="14" t="inlineStr">
+        <is>
+          <t>何必 ends with 呢, not 吗.</t>
+        </is>
+      </c>
+      <c r="L139" s="14" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U12-3</t>
+        </is>
+      </c>
+      <c r="B140" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="C140" s="14" t="inlineStr">
+        <is>
+          <t>辨析</t>
+        </is>
+      </c>
+      <c r="D140" s="14" t="inlineStr">
+        <is>
+          <t>别说一千块了，___一百块我也没有。</t>
+        </is>
+      </c>
+      <c r="E140" s="14" t="inlineStr">
+        <is>
+          <t>但是</t>
+        </is>
+      </c>
+      <c r="F140" s="14" t="inlineStr">
+        <is>
+          <t>还是</t>
+        </is>
+      </c>
+      <c r="G140" s="14" t="inlineStr">
+        <is>
+          <t>只是</t>
+        </is>
+      </c>
+      <c r="H140" s="14" t="inlineStr">
+        <is>
+          <t>就是</t>
+        </is>
+      </c>
+      <c r="I140" s="14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J140" s="14" t="inlineStr">
+        <is>
+          <t>“别说A，就是B也……”，B是更容易的情况，用“就是”引出。</t>
+        </is>
+      </c>
+      <c r="K140" s="14" t="inlineStr">
+        <is>
+          <t>In 别说A，就是B也……, 就是 brings in the easier case B.</t>
+        </is>
+      </c>
+      <c r="L140" s="14" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U12-3</t>
+        </is>
+      </c>
+      <c r="B141" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="C141" s="14" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="D141" s="14" t="inlineStr">
+        <is>
+          <t>这个字太难了，别说外国学生，就是___。</t>
+        </is>
+      </c>
+      <c r="E141" s="14" t="inlineStr">
+        <is>
+          <t>学过的人都认识</t>
+        </is>
+      </c>
+      <c r="F141" s="14" t="inlineStr">
+        <is>
+          <t>中国人也不一定认识</t>
+        </is>
+      </c>
+      <c r="G141" s="14" t="inlineStr">
+        <is>
+          <t>小孩子也会写</t>
+        </is>
+      </c>
+      <c r="H141" s="14" t="inlineStr">
+        <is>
+          <t>外国学生也不认识</t>
+        </is>
+      </c>
+      <c r="I141" s="14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J141" s="14" t="inlineStr">
+        <is>
+          <t>“就是”后面应该是最不可能出问题的人，字很难，连中国人都不一定认识。</t>
+        </is>
+      </c>
+      <c r="K141" s="14" t="inlineStr">
+        <is>
+          <t>就是 introduces the least likely case: even Chinese people may not know such a hard character.</t>
+        </is>
+      </c>
+      <c r="L141" s="14" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U12-3</t>
+        </is>
+      </c>
+      <c r="B142" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="C142" s="14" t="inlineStr">
+        <is>
+          <t>找错</t>
+        </is>
+      </c>
+      <c r="D142" s="14" t="inlineStr">
+        <is>
+          <t>下面哪一句有错？</t>
+        </is>
+      </c>
+      <c r="E142" s="14" t="inlineStr">
+        <is>
+          <t>别说出国了，就是去北京我也没去过。</t>
+        </is>
+      </c>
+      <c r="F142" s="14" t="inlineStr">
+        <is>
+          <t>我太累了，别说跑步，就是走路也不想走。</t>
+        </is>
+      </c>
+      <c r="G142" s="14" t="inlineStr">
+        <is>
+          <t>别说一公里，就是十公里我也跑不了。</t>
+        </is>
+      </c>
+      <c r="H142" s="14" t="inlineStr">
+        <is>
+          <t>这件事别说他了，就是老师也不知道。</t>
+        </is>
+      </c>
+      <c r="I142" s="14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J142" s="14" t="inlineStr">
+        <is>
+          <t>“别说”后面应是更难的，“就是”后面是更容易的：别说十公里，就是一公里我也跑不了。</t>
+        </is>
+      </c>
+      <c r="K142" s="14" t="inlineStr">
+        <is>
+          <t>别说 takes the harder case and 就是 the easier: 别说十公里，就是一公里……</t>
+        </is>
+      </c>
+      <c r="L142" s="14" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U12-4</t>
+        </is>
+      </c>
+      <c r="B143" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="C143" s="14" t="inlineStr">
+        <is>
+          <t>辨析</t>
+        </is>
+      </c>
+      <c r="D143" s="14" t="inlineStr">
+        <is>
+          <t>他___住在上海，没搬过家。</t>
+        </is>
+      </c>
+      <c r="E143" s="14" t="inlineStr">
+        <is>
+          <t>往往</t>
+        </is>
+      </c>
+      <c r="F143" s="14" t="inlineStr">
+        <is>
+          <t>不断</t>
+        </is>
+      </c>
+      <c r="G143" s="14" t="inlineStr">
+        <is>
+          <t>一直</t>
+        </is>
+      </c>
+      <c r="H143" s="14" t="inlineStr">
+        <is>
+          <t>常常</t>
+        </is>
+      </c>
+      <c r="I143" s="14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J143" s="14" t="inlineStr">
+        <is>
+          <t>“一直”表示状态持续不变；“不断”表示动作反复或变化不停，不能说“不断住”；“常常、往往”说的是经常发生的事，跟“没搬过家”不配。</t>
+        </is>
+      </c>
+      <c r="K143" s="14" t="inlineStr">
+        <is>
+          <t>一直 is for an unbroken state; 不断 is for repeated actions or ongoing change; 常常/往往 are for things that happen often, which clashes with never having moved.</t>
+        </is>
+      </c>
+      <c r="L143" s="14" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U12-4</t>
+        </is>
+      </c>
+      <c r="B144" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="C144" s="14" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="D144" s="14" t="inlineStr">
+        <is>
+          <t>这几年，他的中文水平不断___。</t>
+        </is>
+      </c>
+      <c r="E144" s="14" t="inlineStr">
+        <is>
+          <t>很高</t>
+        </is>
+      </c>
+      <c r="F144" s="14" t="inlineStr">
+        <is>
+          <t>好</t>
+        </is>
+      </c>
+      <c r="G144" s="14" t="inlineStr">
+        <is>
+          <t>提高</t>
+        </is>
+      </c>
+      <c r="H144" s="14" t="inlineStr">
+        <is>
+          <t>不错</t>
+        </is>
+      </c>
+      <c r="I144" s="14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J144" s="14" t="inlineStr">
+        <is>
+          <t>“不断”后面跟表示变化的动词，不能跟形容词。</t>
+        </is>
+      </c>
+      <c r="K144" s="14" t="inlineStr">
+        <is>
+          <t>不断 is followed by a verb of change, not an adjective.</t>
+        </is>
+      </c>
+      <c r="L144" s="14" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="14" t="inlineStr">
+        <is>
+          <t>DC4-U12-4</t>
+        </is>
+      </c>
+      <c r="B145" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="C145" s="14" t="inlineStr">
+        <is>
+          <t>找错</t>
+        </is>
+      </c>
+      <c r="D145" s="14" t="inlineStr">
+        <is>
+          <t>下面哪一句有错？</t>
+        </is>
+      </c>
+      <c r="E145" s="14" t="inlineStr">
+        <is>
+          <t>他不断是我最好的朋友。</t>
+        </is>
+      </c>
+      <c r="F145" s="14" t="inlineStr">
+        <is>
+          <t>他一直在等你的电话。</t>
+        </is>
+      </c>
+      <c r="G145" s="14" t="inlineStr">
+        <is>
+          <t>这几年，来这儿旅游的人不断增加。</t>
+        </is>
+      </c>
+      <c r="H145" s="14" t="inlineStr">
+        <is>
+          <t>最近的天气一直不太好。</t>
+        </is>
+      </c>
+      <c r="I145" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J145" s="14" t="inlineStr">
+        <is>
+          <t>“是”表示状态，要用“一直”：他一直是我最好的朋友。</t>
+        </is>
+      </c>
+      <c r="K145" s="14" t="inlineStr">
+        <is>
+          <t>是 describes a state, so use 一直.</t>
+        </is>
+      </c>
+      <c r="L145" s="14" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:Q49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -11531,7 +19696,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11858,13 +20023,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -12015,12 +20180,24 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>进阶练习（网站，2026-10）</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>「进阶练习」表是为网站新写的进阶题：每个语法点辨析选择、完成句子、找错各 1 道（点选作答，带中英文解析；入门册另附题干英文），难度按本册水平控制，经出题、正确性+难度审核、终审三轮把关。网站上它们替换了 01 表「练习1–3」中的填空/选择/排序等题；翻译题保留，其中答案与例句完全相同的，在本表换成了新句子（题型=翻译）。01 表原有练习未改动。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
